--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X86"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688856644818249</t>
+          <t>1688858289869798</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -677,17 +677,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -708,7 +708,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -732,32 +732,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854894759558</t>
+          <t>1688857703847806</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -769,24 +769,29 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -807,7 +812,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -831,32 +836,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688854776688740</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -868,11 +873,11 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -880,17 +885,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -911,7 +916,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -935,7 +940,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688854470818602</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -945,22 +950,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -975,12 +980,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>17,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -989,12 +989,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1015,7 +1015,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1039,32 +1039,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688855270890428</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1172,32 +1172,42 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>刘佳宁</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>liujianing</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1218,7 +1228,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1242,32 +1252,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688857455845397</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1279,29 +1289,24 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1322,7 +1327,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1346,32 +1351,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688856312814793</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1390,17 +1395,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1421,7 +1426,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1445,32 +1450,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1489,17 +1494,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1520,7 +1525,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1544,32 +1549,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688855270890461</t>
+          <t>1688858008853709</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1581,29 +1586,29 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>魏布婷</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>weibuting</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1624,7 +1629,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1648,32 +1653,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1685,11 +1690,11 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -1697,17 +1702,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1728,7 +1733,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1752,32 +1757,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1796,17 +1801,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1827,7 +1832,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1851,32 +1856,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688854894759430</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1895,17 +1900,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1926,7 +1931,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1950,32 +1955,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688857372708211</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1994,17 +1999,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2025,7 +2030,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2049,32 +2054,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2086,24 +2091,29 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2124,7 +2134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2148,32 +2158,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688854476856492</t>
+          <t>1688854706800124</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2192,17 +2202,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2223,7 +2233,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2247,32 +2257,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2291,17 +2301,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2322,7 +2332,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2346,32 +2356,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688855270890470</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2395,17 +2405,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2426,7 +2436,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2450,32 +2460,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857751871176</t>
+          <t>1688854476856492</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2487,24 +2497,29 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
+        </is>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>吕怡萱</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>lvyixuan</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2525,7 +2540,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2549,32 +2564,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688855270890478</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2586,11 +2601,11 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2598,17 +2613,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>朱鑫磊</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>zhuxinlei</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2629,7 +2644,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2653,7 +2668,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688854894759558</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2663,22 +2678,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2702,12 +2717,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2728,7 +2743,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2752,32 +2767,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688858124858984</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2789,24 +2804,29 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2827,7 +2847,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2851,32 +2871,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688854281870550</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2888,24 +2908,29 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,17,18</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2926,7 +2951,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2950,7 +2975,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688855270890446</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2965,17 +2990,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3004,12 +3029,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3030,7 +3055,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3054,32 +3079,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688856644818249</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3098,17 +3123,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3129,7 +3154,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3153,32 +3178,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688855070755789</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3197,17 +3222,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3228,7 +3253,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3252,7 +3277,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688857755978271</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3262,22 +3287,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3289,7 +3314,12 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>9,10,11,12,13,14,15,16</t>
+        </is>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
@@ -3301,12 +3331,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>范夺</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>fanduo</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3327,7 +3357,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3351,7 +3381,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688854815837469</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3366,17 +3396,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3385,28 +3415,13 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3415,12 +3430,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3441,7 +3456,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3465,32 +3480,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688857145762192</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3509,17 +3524,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3540,7 +3555,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3564,7 +3579,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688854575781532</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3579,17 +3594,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3601,12 +3616,7 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -3618,12 +3628,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3644,7 +3654,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3668,32 +3678,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688855477810382</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3705,29 +3715,24 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3748,7 +3753,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3772,7 +3777,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3782,22 +3787,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3809,12 +3814,7 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
@@ -3826,12 +3826,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3852,7 +3852,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3876,32 +3876,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688854603884803</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3951,7 +3951,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3975,32 +3975,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688855600786055</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4012,29 +4012,29 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q35" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688857145762192</t>
+          <t>1688854497763413</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4154,7 +4154,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4178,32 +4178,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4215,24 +4215,29 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4253,7 +4258,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4277,7 +4282,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688857392814199</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4287,22 +4292,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4326,12 +4331,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4352,7 +4357,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4376,32 +4381,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688856312814793</t>
+          <t>1688855600786055</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4416,21 +4421,26 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4451,7 +4461,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4475,32 +4485,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688854706799328</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4512,24 +4522,29 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,19,20,21</t>
+        </is>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4550,7 +4565,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4574,32 +4589,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688855086834341</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4618,17 +4633,17 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4649,7 +4664,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4673,7 +4688,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688856443851799</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4683,22 +4698,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4710,12 +4725,7 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
@@ -4727,12 +4737,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>闫刘梦</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>yanliumeng</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4753,7 +4763,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4777,32 +4787,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688856736832479</t>
+          <t>1688855270890436</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4814,11 +4824,11 @@
         <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -4826,17 +4836,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>曹钰淼</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>caoyumiao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4857,7 +4867,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4881,32 +4891,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688854522754461</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4918,11 +4928,11 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q44" t="n">
@@ -4930,17 +4940,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4961,7 +4971,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4985,7 +4995,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688857372708211</t>
+          <t>1688854761929635</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4995,22 +5005,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5022,7 +5032,12 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
@@ -5034,12 +5049,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5060,7 +5075,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5084,32 +5099,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688857455845397</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5121,24 +5136,29 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>张迎</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>zhangying04</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5159,7 +5179,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5183,32 +5203,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688854603884803</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5220,11 +5240,11 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5232,17 +5252,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5263,7 +5283,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5287,32 +5307,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688856443851784</t>
+          <t>1688856819940740</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5327,26 +5347,21 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>蒋明阳</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>jiangmingyang</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5367,7 +5382,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5391,32 +5406,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688854522754461</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5428,29 +5443,24 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5471,7 +5481,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5495,32 +5505,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688855473818358</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5532,24 +5542,29 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5570,7 +5585,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5594,32 +5609,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688855473818358</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5638,17 +5653,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5669,7 +5684,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5693,32 +5708,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688854706800124</t>
+          <t>1688855270890446</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5730,24 +5745,29 @@
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5768,7 +5788,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5792,32 +5812,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5829,11 +5849,11 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.3888888888888889</v>
+        <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -5841,17 +5861,17 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5872,7 +5892,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5896,32 +5916,32 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5933,24 +5953,29 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,23</t>
+        </is>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5971,7 +5996,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5995,7 +6020,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6005,22 +6030,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6044,12 +6069,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6070,7 +6095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6094,32 +6119,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6131,24 +6156,29 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6169,7 +6199,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6193,32 +6223,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6230,29 +6260,24 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6273,7 +6298,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6312,7 +6337,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -6372,7 +6397,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6396,32 +6421,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688855770825227</t>
+          <t>1688855827846478</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6430,32 +6455,42 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>11,12,13</t>
+        </is>
       </c>
       <c r="O59" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>11,12,13</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>梁秀枝</t>
+          <t>王旭炀</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>liangxiuzhi</t>
+          <t>wangxuyang01</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6476,7 +6511,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6500,32 +6535,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688854706799328</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6537,29 +6572,24 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6580,7 +6610,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6604,32 +6634,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688854281870530</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6653,17 +6683,17 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6684,7 +6714,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6708,32 +6738,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6745,34 +6775,24 @@
         <v>1</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>17,20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6793,7 +6813,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6817,32 +6837,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6854,24 +6874,29 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6892,7 +6917,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20260911</v>
+        <v>20260918</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6916,32 +6941,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688854776688740</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6953,29 +6978,29 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+        </is>
       </c>
       <c r="Q64" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>15,22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6989,2244 +7014,6 @@
         </is>
       </c>
       <c r="X64" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1688854287853916</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>谷豪华</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>guhaohua</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M65" t="n">
-        <v>1</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>1</v>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>谷豪华</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>guhaohua</t>
-        </is>
-      </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>1688854497763413</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>姜傲爽</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>jiangaoshuang</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>1</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>姜傲爽</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>jiangaoshuang</t>
-        </is>
-      </c>
-      <c r="V66" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>1688854476856420</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>李雨薇</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>liyuwei</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>1</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>李雨薇</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>liyuwei</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>1688854894759300</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>吕禛杨</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>lvzhenyang</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>吕禛杨</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>lvzhenyang</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>1688855292870141</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>赵世文</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>zhaoshiwen</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M69" t="n">
-        <v>1</v>
-      </c>
-      <c r="O69" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>赵世文</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>zhaoshiwen</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>1688857951732153</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>李肖雨</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>lixiaoyu</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>0元</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
-        <v>1</v>
-      </c>
-      <c r="O70" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>李肖雨</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>lixiaoyu</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>1688857703847806</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>卫晓迪</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>weixiaodi</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>1</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>卫晓迪</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>weixiaodi</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>1688854522754143</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>张波</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>zhangbo</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>张波</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>zhangbo</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>1688854815837469</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>张菁</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>zhangjing03</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>1</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>张菁</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>zhangjing03</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>高中</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>1688857951732153</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>李肖雨</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>lixiaoyu</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M74" t="n">
-        <v>1</v>
-      </c>
-      <c r="O74" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>1</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>李肖雨</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>lixiaoyu</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>1688858275775684</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>WFCPeak</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>刘世乐</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>liushile</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>1</v>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>刘世乐</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>liushile</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>1688854470818602</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>孙宇哲</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>sunyuzhe</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>孙宇哲</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>sunyuzhe</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>1688858008853709</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>耿亚轩</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>gengyaxuan</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>耿亚轩</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>gengyaxuan</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>1688854894759430</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>黄诺</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>huangnuo</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
-      </c>
-      <c r="O78" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>1</v>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>黄诺</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>huangnuo</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>1688855593838985</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>彭涛</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>pengtao</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="O79" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>1</v>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>彭涛</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>pengtao</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>1688856995795370</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>WFCPeak</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>赵晨曦</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>zhaochenxi</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>赵晨曦</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>zhaochenxi</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>1688855827846478</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>王旭炀</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>wangxuyang01</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M81" t="n">
-        <v>1</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>22,23</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>王旭炀</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>wangxuyang01</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>1688857751871228</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>汪光磊</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>wangguanglei</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M82" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q82" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>汪光磊</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>wangguanglei</t>
-        </is>
-      </c>
-      <c r="V82" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>1688856920865401</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>刘晓松</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>liuxiaosong</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="O83" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Q83" t="n">
-        <v>1</v>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>刘晓松</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>liuxiaosong</t>
-        </is>
-      </c>
-      <c r="V83" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>1688854498774486</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>高梓慧</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>gaozihui</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="O84" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>1</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>高梓慧</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>gaozihui</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>1688855070755789</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>严绍源</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>yanshaoyuan</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
-      </c>
-      <c r="Q85" t="n">
-        <v>1</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>严绍源</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>yanshaoyuan</t>
-        </is>
-      </c>
-      <c r="V85" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>20260911</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>1688856819940740</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>芦凯</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>lukai</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>1</v>
-      </c>
-      <c r="O86" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>1</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T86" t="inlineStr">
-        <is>
-          <t>芦凯</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>lukai</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -9243,7 +7030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9305,19 +7092,19 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -9333,19 +7120,19 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
         <v>11</v>
       </c>
-      <c r="E3" t="n">
-        <v>8</v>
-      </c>
       <c r="F3" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -9365,19 +7152,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="5">
@@ -9406,10 +7193,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="6">
@@ -9425,19 +7212,19 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E6" t="n">
         <v>23</v>
       </c>
       <c r="F6" t="n">
-        <v>0.92</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -9453,23 +7240,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -9485,23 +7272,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -9512,28 +7299,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
+          <t>初二 汇总</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="10">
@@ -9544,24 +7327,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>初二 汇总</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
       <c r="D10" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G10" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="11">
@@ -9572,28 +7359,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="12">
@@ -9604,84 +7387,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
-        </is>
-      </c>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9365079365079365</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>19</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>初中 汇总</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>90</v>
-      </c>
-      <c r="E14" t="n">
-        <v>75</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G14" t="n">
-        <v>53</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5888888888888889</v>
+        <v>0.5396825396825397</v>
       </c>
     </row>
   </sheetData>
@@ -9695,7 +7418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9711,7 +7434,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-9月10日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-9月14日</t>
         </is>
       </c>
     </row>
@@ -9792,19 +7515,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="F4" s="5" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -9820,19 +7543,19 @@
       </c>
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>8</v>
-      </c>
       <c r="F5" s="7" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -9852,19 +7575,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>13</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.9285714285714286</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="7">
@@ -9893,10 +7616,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="8">
@@ -9912,19 +7635,19 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>23</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.92</v>
+        <v>0.9583333333333334</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4166666666666667</v>
       </c>
     </row>
     <row r="9">
@@ -9940,23 +7663,23 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -9972,203 +7695,139 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4" t="n">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>初二 汇总</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="H11" s="5" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>初二 汇总</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr"/>
-      <c r="D12" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="E12" s="6" t="n">
+      <c r="E12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr"/>
+      <c r="D13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0.9365079365079365</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>0.9714285714285714</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>27</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F13" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>蒸蒸日上-兴-刘亚雄</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="n">
-        <v>19</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0.3157894736842105</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>初中 汇总</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0.5888888888888889</v>
+      <c r="H14" s="7" t="n">
+        <v>0.5396825396825397</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -7336,19 +7336,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G10" t="n">
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="11">
@@ -7364,19 +7364,19 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
         <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="12">
@@ -7392,19 +7392,19 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E12" t="n">
         <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="G12" t="n">
         <v>34</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.4533333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -7759,19 +7759,19 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>7</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="13">
@@ -7787,19 +7787,19 @@
       </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>7</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.2380952380952381</v>
       </c>
     </row>
     <row r="14">
@@ -7815,19 +7815,19 @@
       </c>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>59</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.9365079365079365</v>
+        <v>0.7866666666666666</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>34</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.5396825396825397</v>
+        <v>0.4533333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,66 +628,64 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1688858289869798</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1688854894759300</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>吕禛杨</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>lvzhenyang</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>冯一帆</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fengyifan01</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -727,37 +725,35 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1688857703847806</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1688854281870569</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -781,17 +777,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -831,37 +827,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1688854776688740</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1688858289869798</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -873,11 +867,11 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+          <t>22,23</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -885,17 +879,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -935,37 +929,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>1688854470818602</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1688854603884803</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -984,17 +976,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1024,7 +1016,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>短期班</t>
+          <t>长期班</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1034,37 +1026,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1688858199721276</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1688855600786055</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1073,27 +1063,42 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>曹晓雨</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>caoxiaoyu</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1133,37 +1138,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1688858124858856</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1688854776688740</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1172,42 +1175,27 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1247,66 +1235,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1688855928851644</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1688857751871196</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>杨佳雪</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>yangjiaxue</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>杨璐</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>yanglu</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1346,37 +1332,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1688856312814793</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1688854894759481</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1385,27 +1369,42 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1445,37 +1444,35 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1688854894759300</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1688854281870561</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1487,24 +1484,29 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1544,37 +1546,35 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>1688858008853709</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1688857392814199</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1589,26 +1589,21 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1648,71 +1643,64 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1688854287853916</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1688856624782683</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>张硕辉</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>zhangshuohui01</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>谷豪华</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>guhaohua</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1752,37 +1740,35 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1688854522754361</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1688857703847806</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1794,24 +1780,29 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1851,37 +1842,35 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1688854894759430</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1688856819940740</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1900,17 +1889,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1950,37 +1939,35 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>1688857372708211</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1688855270890491</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1992,24 +1979,29 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2049,37 +2041,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1688854281870561</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1688857790837398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2088,32 +2078,42 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2153,37 +2153,35 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>1688854706800124</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1688856261784494</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2195,24 +2193,29 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2252,66 +2255,69 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1688855770825630</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1688856920865401</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>刘晓松</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>liuxiaosong</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>高佳华</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>gaojiahua</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2351,37 +2357,35 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1688855270890470</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1688854497763413</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2393,29 +2397,24 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2455,37 +2454,35 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>1688854476856492</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1688854815837469</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2497,29 +2494,24 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2559,37 +2551,35 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>1688855593838985</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1688855686929440</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2601,11 +2591,11 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2613,17 +2603,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2663,66 +2653,64 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1688854894759558</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1688855581862225</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>张子璇</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>zhangzixuan03</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>胡茹茹</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>hururu</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2762,37 +2750,35 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1688858124858984</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1688857145762192</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2804,29 +2790,24 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2866,71 +2847,64 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>1688854281870550</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1688854476856420</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>李雨薇</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>liyuwei</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
           <t>初一</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>王紫东</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>wangzidong</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,17,18</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2970,37 +2944,35 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>1688855270890491</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1688854575781532</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3012,29 +2984,29 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3074,37 +3046,35 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>1688856644818249</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1688854522754461</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3116,24 +3086,29 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3173,37 +3148,35 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1688855070755789</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1688854281870530</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3215,24 +3188,29 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3272,71 +3250,64 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1688855581862225</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1688855928851644</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>杨璐</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>yanglu</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>张子璇</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>zhangzixuan03</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3376,37 +3347,35 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1688854815837469</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1688858124858984</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3418,24 +3387,29 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>10,11</t>
+        </is>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3475,37 +3449,35 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>1688857145762192</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1688854784881054</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3517,24 +3489,29 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3574,13 +3551,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>1688854575781532</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1688854784881058</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3594,17 +3569,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3616,7 +3591,12 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
@@ -3628,12 +3608,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3673,37 +3653,35 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1688855477810382</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1688857605746717</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3722,17 +3700,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3772,66 +3750,64 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1688857691776053</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1688856312814793</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>张瑶森</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>zhangyaosen</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>张亮亮</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>zhangliangliang</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张瑶森</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangyaosen</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3871,66 +3847,64 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1688854522753923</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1688854476856492</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>张一卓</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>zhangyizhuo01</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>刘莹凤</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>liuyingfeng</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3970,71 +3944,64 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1688854287853891</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1688855770825630</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>高佳华</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>gaojiahua</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>牛威</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>niuwei</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4074,37 +4041,35 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1688854497763413</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1688857372708211</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4123,17 +4088,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4173,37 +4138,35 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1688858124858906</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1688855270890436</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4227,17 +4190,17 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4277,66 +4240,64 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1688857392814199</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1688855086834341</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>魏晨阳</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>weichenyang</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>申谭谭</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>shentantan</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4376,37 +4337,35 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>1688855600786055</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1688855270890470</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4418,29 +4377,29 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q39" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4480,37 +4439,35 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1688856920865401</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1688854281870550</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4522,11 +4479,11 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.5</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,19,20,21</t>
+          <t>9,10</t>
         </is>
       </c>
       <c r="Q40" t="n">
@@ -4534,17 +4491,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4584,37 +4541,35 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>1688855086834341</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1688855270890446</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4626,24 +4581,29 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q41" t="n">
         <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4683,66 +4643,64 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1688857254754511</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1688854894759558</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>胡茹茹</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>hururu</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>云程发轫</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>李旭东</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>lixudong</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4782,71 +4740,64 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>1688855270890436</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1688855477810382</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>李奕昕</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>liyixin</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
           <t>初一</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>重装五组</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>张学伦</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>zhangxuelun01</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>1</v>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>初一</t>
-        </is>
-      </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4886,37 +4837,35 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>1688854522754461</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1688857254754511</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4928,29 +4877,24 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4990,71 +4934,64 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1688854761929635</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1688854497763364</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>杨博岚</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>yangbolan</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>张亦浩</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>zhangyihao</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5094,13 +5031,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>1688857455845397</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1688854784881061</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5114,17 +5049,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5153,12 +5088,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5198,37 +5133,35 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>1688854603884803</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1688854706800124</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5240,29 +5173,24 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5302,13 +5230,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>1688856819940740</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1688854784881036</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5322,17 +5248,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5344,7 +5270,12 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -5356,12 +5287,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5401,37 +5332,35 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>1688854497763364</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1688855593838985</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5443,24 +5372,29 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14</t>
+        </is>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5500,71 +5434,69 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1688855564781214</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1688854761929635</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>张亦浩</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>zhangyihao</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>10,11,12,13,14,15,16,17</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>陈利辉</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>chenlihui</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5604,66 +5536,64 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>1688855473818358</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1688854260743321</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>杨鹏飞</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>yangpengfei</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>天天向上</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>吴相宏</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>wuxianghong02</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>1</v>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5703,71 +5633,64 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>1688855270890446</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1688854470818602</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>孙宇哲</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>sunyuzhe</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>谷晨旭</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>guchenxu</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M52" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5807,37 +5730,35 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>1688854281870569</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1688857691776053</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5849,29 +5770,24 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5911,37 +5827,35 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1688855292870141</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1688856261784534</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5953,11 +5867,11 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0.6111111111111112</v>
+        <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>14,15,16,17,18,19,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -5965,17 +5879,17 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6015,37 +5929,35 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>1688857605746717</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1688854287853916</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6054,27 +5966,42 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6114,37 +6041,35 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>1688854260743321</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1688856644818249</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6156,29 +6081,24 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6218,66 +6138,64 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>1688857751871196</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1688855070755789</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>严绍源</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>yanshaoyuan</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
           <t>初二</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>超级莱米</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>杨佳雪</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>yangjiaxue</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>1</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>初二</t>
-        </is>
-      </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6317,66 +6235,64 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1688854572834470</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1688855473818358</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>吴相宏</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>wuxianghong02</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>张浩</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>zhanghao06</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M58" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>1</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>初三</t>
-        </is>
-      </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>吴相宏</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>wuxianghong02</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6416,37 +6332,35 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>1688855827846478</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1688854522754143</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6455,42 +6369,27 @@
         </is>
       </c>
       <c r="M59" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6530,13 +6429,11 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>1688854706799328</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1688857790837033</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6550,17 +6447,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6572,7 +6469,12 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -6584,12 +6486,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6629,37 +6531,35 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>1688854281870530</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1688858199721276</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6671,29 +6571,24 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6733,37 +6628,35 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>1688854522754143</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1688854706799328</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6782,17 +6675,17 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6832,37 +6725,35 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>1688854476856420</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1688857790837332</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6874,11 +6765,11 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
         </is>
       </c>
       <c r="Q63" t="n">
@@ -6886,17 +6777,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6936,84 +6827,1393 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1688856624782683</t>
-        </is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1688855564781214</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>1</v>
+      </c>
+      <c r="O64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>陈利辉</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>chenlihui</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1688855292870141</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>赵世文</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>zhaoshiwen</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>赵世文</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>zhaoshiwen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1688854894759430</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>huangnuo</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>黄诺</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>huangnuo</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1688858008853709</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>耿亚轩</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>gengyaxuan</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>耿亚轩</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>gengyaxuan</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1688854784881034</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1688855827846478</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>wangxuyang01</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,22,23</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>王旭炀</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>wangxuyang01</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1688854572834470</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1688854522754361</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>1</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>张鑫禹</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>zhangxinyu01</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1688854522753923</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>刘莹凤</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>liuyingfeng</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>刘莹凤</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>liuyingfeng</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1688858124858856</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>王佳琦</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>wangjiaqi05</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>王佳琦</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>wangjiaqi05</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1688854287853891</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>niuwei</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>牛威</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>niuwei</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1688858124858906</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t>天天向上</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>张硕辉</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>zhangshuohui01</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>刘晓娜</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>liuxiaona</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="S64" t="inlineStr">
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="inlineStr">
         <is>
           <t>初三</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>张硕辉</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>zhangshuohui01</t>
-        </is>
-      </c>
-      <c r="V64" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>刘晓娜</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>liuxiaona</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1688857455845397</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>zhangying04</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>9,10,11,12,13,14,15,16,22</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>张迎</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>zhangying04</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>20260918</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1688854784881059</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>仲欣琦</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>zhongxinqi</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>1</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>仲欣琦</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>zhongxinqi</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -7095,16 +8295,16 @@
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -7123,16 +8323,16 @@
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -7155,16 +8355,16 @@
         <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="5">
@@ -7193,10 +8393,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="6">
@@ -7215,16 +8415,16 @@
         <v>24</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -7279,16 +8479,16 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="9">
@@ -7307,16 +8507,16 @@
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="10">
@@ -7339,16 +8539,16 @@
         <v>21</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="11">
@@ -7367,16 +8567,16 @@
         <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="12">
@@ -7395,16 +8595,16 @@
         <v>75</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7434,7 +8634,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-9月14日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-9月16日</t>
         </is>
       </c>
     </row>
@@ -7518,16 +8718,16 @@
         <v>12</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -7546,16 +8746,16 @@
         <v>12</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -7578,16 +8778,16 @@
         <v>13</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="7">
@@ -7616,10 +8816,10 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.4545454545454545</v>
       </c>
     </row>
     <row r="8">
@@ -7638,16 +8838,16 @@
         <v>24</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.875</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="9">
@@ -7702,16 +8902,16 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="11">
@@ -7730,16 +8930,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="12">
@@ -7762,16 +8962,16 @@
         <v>21</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="13">
@@ -7790,16 +8990,16 @@
         <v>21</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="14">
@@ -7818,16 +9018,16 @@
         <v>75</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>0.4533333333333333</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X77"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -631,32 +631,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1688854894759300</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1688854287853916</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -668,24 +670,29 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -706,7 +713,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -728,32 +735,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1688854281870569</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1688854784881058</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -777,17 +786,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -808,7 +817,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -830,8 +839,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1688858289869798</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1688857254754511</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -840,22 +851,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -867,11 +878,11 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>22,23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -884,12 +895,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -910,7 +921,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -932,32 +943,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1688854603884803</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1688857691776053</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -976,17 +989,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1007,7 +1020,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1016,7 +1029,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>长期班</t>
+          <t>短期班</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1029,32 +1042,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1688855600786055</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1688855086834341</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1063,42 +1078,27 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>曹晓雨</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>caoxiaoyu</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1119,7 +1119,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1141,32 +1141,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1688854776688740</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1688857167940654</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1178,24 +1180,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1216,7 +1223,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1238,8 +1245,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1688857751871196</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1688855564781214</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1253,17 +1262,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1287,12 +1296,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1313,7 +1322,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1335,32 +1344,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1688854894759481</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1688854287853891</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1369,42 +1380,27 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1425,7 +1421,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1447,32 +1443,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1688854281870561</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1688855581862225</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1484,11 +1482,11 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1496,17 +1494,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1527,7 +1525,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1549,8 +1547,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1688857392814199</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1688857452809589</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1624,7 +1624,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1646,32 +1646,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1688856624782683</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1688854281870599</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1690,17 +1692,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1721,7 +1723,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1743,32 +1745,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1688857703847806</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1688854894759300</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1780,29 +1784,24 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1823,7 +1822,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1845,32 +1844,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>1688856819940740</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1688854281870561</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1889,17 +1890,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1920,7 +1921,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1942,32 +1943,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>1688855270890491</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1688855270890436</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1979,29 +1982,24 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2022,7 +2020,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2044,32 +2042,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1688857790837398</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1688856920865401</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2078,42 +2078,32 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2134,7 +2124,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2156,32 +2146,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>1688856261784494</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1688854761929635</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2193,29 +2185,24 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2236,7 +2223,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2258,32 +2245,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>1688856920865401</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1688854281870550</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2295,29 +2284,29 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2338,7 +2327,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2360,32 +2349,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>1688854497763413</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1688855270890512</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2404,17 +2395,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2435,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2457,32 +2448,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1688854815837469</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1688854784881054</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2501,17 +2494,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2532,7 +2525,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2554,32 +2547,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>1688855686929440</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1688857605746717</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2591,29 +2586,24 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2634,7 +2624,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2656,8 +2646,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>1688855581862225</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1688858289869798</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -2671,17 +2663,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2705,12 +2697,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2731,7 +2723,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2753,32 +2745,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>1688857145762192</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1688857751871196</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2797,17 +2791,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2828,7 +2822,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2850,8 +2844,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1688854476856420</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1688858124858984</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2865,17 +2861,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2899,12 +2895,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2925,7 +2921,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2947,32 +2943,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>1688854575781532</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1688856624782683</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2987,26 +2985,21 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3027,7 +3020,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3049,32 +3042,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>1688854522754461</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1688854287853876</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3086,29 +3081,24 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3129,7 +3119,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3151,32 +3141,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1688854281870530</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1688857790837332</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3200,17 +3192,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3231,7 +3223,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3253,8 +3245,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1688855928851644</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1688855070755789</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3263,22 +3257,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3287,13 +3281,28 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3302,12 +3311,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3328,7 +3337,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3350,32 +3359,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>1688858124858984</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1688855770825630</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3387,29 +3398,24 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3430,7 +3436,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3452,32 +3458,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1688854784881054</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1688855477810382</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3489,29 +3497,24 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3532,7 +3535,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3554,32 +3557,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1688854784881058</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1688854572834470</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3591,29 +3596,24 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3634,7 +3634,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3656,8 +3656,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1688857605746717</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1688857167940610</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3666,22 +3668,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3693,7 +3695,12 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -3705,12 +3712,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3731,7 +3738,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3753,32 +3760,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1688856312814793</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1688856475868784</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3797,17 +3806,17 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>张瑶森</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhangyaosen</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3828,7 +3837,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3850,32 +3859,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1688854476856492</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1688855593838985</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3894,17 +3905,17 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3925,7 +3936,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3947,32 +3958,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1688855770825630</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1688854281870569</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3984,24 +3997,29 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4022,7 +4040,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4044,32 +4062,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1688857372708211</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1688857790837033</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4081,24 +4101,29 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4119,7 +4144,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4141,32 +4166,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1688855270890436</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1688855270890446</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4178,29 +4205,24 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4221,7 +4243,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4243,8 +4265,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1688855086834341</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1688854784881059</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4253,22 +4277,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4280,7 +4304,12 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -4292,12 +4321,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4318,7 +4347,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4340,32 +4369,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>1688855270890470</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1688855001729346,1688854706799328</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4377,29 +4408,24 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4420,7 +4446,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4442,32 +4468,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>1688854281870550</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1688854476856492</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4479,29 +4507,24 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4522,7 +4545,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4544,32 +4567,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1688855270890446</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1688857167940672</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4581,11 +4606,11 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,21,22,23</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -4593,17 +4618,17 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4624,7 +4649,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4646,8 +4671,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>1688854894759558</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1688854498774486</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4656,22 +4683,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4695,12 +4722,12 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4721,7 +4748,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4743,8 +4770,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1688855477810382</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1688854281870530</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4758,17 +4787,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4792,12 +4821,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4818,7 +4847,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4840,32 +4869,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1688857254754511</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1688855270890491</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4884,17 +4915,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4915,7 +4946,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4937,32 +4968,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>1688854497763364</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1688858199721276</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4981,17 +5014,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5012,7 +5045,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5034,8 +5067,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>1688854784881061</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1688857790837398</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5049,17 +5084,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5071,12 +5106,7 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -5088,12 +5118,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5114,7 +5144,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5136,32 +5166,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>1688854706800124</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1688854522754461</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5173,24 +5205,29 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q47" t="n">
         <v>1</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5211,7 +5248,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5233,8 +5270,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1688854784881036</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1688856261784494</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -5248,17 +5287,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5287,12 +5326,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5313,7 +5352,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5335,8 +5374,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>1688855593838985</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1688855270890470</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -5350,17 +5391,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5372,11 +5413,11 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5389,12 +5430,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5415,7 +5456,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5437,8 +5478,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1688854761929635</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1688854522754143</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -5447,22 +5490,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5474,12 +5517,7 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
@@ -5491,12 +5529,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5517,7 +5555,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5539,32 +5577,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1688854260743321</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1688856995795370</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5583,17 +5623,17 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5614,7 +5654,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5636,32 +5676,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>1688854470818602</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1688854784881061</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5673,24 +5715,29 @@
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5711,7 +5758,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5733,8 +5780,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>1688857691776053</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1688858124858906</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -5748,17 +5797,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5770,7 +5819,12 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -5782,12 +5836,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5808,7 +5862,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5830,32 +5884,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>1688856261784534</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1688855639780332</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5867,29 +5923,24 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5910,7 +5961,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5932,8 +5983,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1688854287853916</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1688854522753923</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -5942,22 +5995,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5966,28 +6019,13 @@
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5996,12 +6034,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6022,7 +6060,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6044,32 +6082,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>1688856644818249</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1688854281870539</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6081,24 +6121,29 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6119,7 +6164,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6141,8 +6186,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1688855070755789</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1688857115860438</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6151,22 +6198,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6190,12 +6237,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6216,7 +6263,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6238,8 +6285,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1688855473818358</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1688858124858856</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6248,22 +6297,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6287,12 +6336,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>吴相宏</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>wuxianghong02</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6313,7 +6362,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6335,8 +6384,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>1688854522754143</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1688854497763364</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6345,22 +6396,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6372,7 +6423,12 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
@@ -6384,12 +6440,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6410,7 +6466,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6432,8 +6488,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>1688857790837033</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1688856311853482</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6447,17 +6505,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6486,12 +6544,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6512,7 +6570,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6534,8 +6592,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>1688858199721276</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1688857751871228</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6549,17 +6609,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6583,12 +6643,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6609,7 +6669,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6631,32 +6691,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>1688854706799328</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1688854894759481</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6675,17 +6737,17 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6706,7 +6768,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6728,32 +6790,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>1688857790837332</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1688854522754361</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6765,29 +6829,24 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6808,7 +6867,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6830,32 +6889,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>1688855564781214</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1688854476856420</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6874,17 +6935,17 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6905,7 +6966,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6927,32 +6988,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>1688855292870141</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1688858275775684</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6964,29 +7027,24 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7007,7 +7065,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -7029,8 +7087,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1688854894759430</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1688855928851644</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -7044,17 +7104,17 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7069,12 +7129,7 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -7083,12 +7138,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7109,7 +7164,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7131,32 +7186,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1688858008853709</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1688855292870141</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7168,24 +7225,29 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>11,12,13,14</t>
+        </is>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7206,7 +7268,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7228,32 +7290,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>1688854784881034</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1688854260743321</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7265,29 +7329,24 @@
         <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q68" t="n">
         <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7308,7 +7367,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7330,32 +7389,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>1688855827846478</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1688854497763413</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7370,26 +7431,21 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>王旭炀</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>wangxuyang01</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7410,7 +7466,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7432,32 +7488,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>1688854572834470</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1688857167940637</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7469,24 +7527,29 @@
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7507,7 +7570,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7529,32 +7592,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>1688854522754361</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1688856819940740</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7573,17 +7638,17 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7604,7 +7669,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7626,32 +7691,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>1688854522753923</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1688857392814199</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7670,17 +7737,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7701,7 +7768,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7723,8 +7790,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>1688858124858856</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1688857452809516</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -7733,22 +7802,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7757,28 +7826,13 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7787,12 +7841,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7813,7 +7867,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -7835,32 +7889,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>1688854287853891</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1688858008853709</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7872,29 +7928,24 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7915,7 +7966,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -7937,32 +7988,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1688858124858906</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1688857609868354</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7974,29 +8027,29 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21</t>
+        </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8017,7 +8070,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -8039,32 +8092,34 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1688857455845397</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1688857752769746</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8076,29 +8131,24 @@
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16,22</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>张迎</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>zhangying04</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8119,7 +8169,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>20260918</v>
+        <v>20261009</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -8141,8 +8191,10 @@
           <t>初阶</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>1688854784881059</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1688854346851430</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -8156,17 +8208,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8195,12 +8247,12 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8214,6 +8266,417 @@
         </is>
       </c>
       <c r="X77" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1688855686929440</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1688856261784534</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>刘佳欣</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>liujiaxin01</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>刘佳欣</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>liujiaxin01</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1688854784881034</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>任超悦</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>renchaoyue</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1688854575781532</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>崔红月</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>cuihongyue</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>17,18</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>崔红月</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>cuihongyue</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -8230,7 +8693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8292,19 +8755,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="3">
@@ -8320,19 +8783,19 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -8352,19 +8815,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8461538461538461</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="5">
@@ -8384,19 +8847,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4545454545454545</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -8412,19 +8875,19 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="7">
@@ -8440,23 +8903,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -8472,23 +8935,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="9">
@@ -8499,24 +8962,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>初二 汇总</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9444444444444444</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="10">
@@ -8527,28 +8994,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8095238095238095</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -8559,24 +9026,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
+          <t>初二 汇总</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6756756756756757</v>
       </c>
     </row>
     <row r="12">
@@ -8587,24 +9054,84 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>初中 汇总</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>75</v>
-      </c>
-      <c r="E12" t="n">
-        <v>67</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.8933333333333333</v>
-      </c>
-      <c r="G12" t="n">
-        <v>42</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5600000000000001</v>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>84</v>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G14" t="n">
+        <v>53</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6309523809523809</v>
       </c>
     </row>
   </sheetData>
@@ -8618,7 +9145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -8634,7 +9161,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-9月16日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-10月8日</t>
         </is>
       </c>
     </row>
@@ -8715,19 +9242,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -8743,19 +9270,19 @@
       </c>
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -8775,19 +9302,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.8461538461538461</v>
+        <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="7">
@@ -8807,19 +9334,19 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>10</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.4545454545454545</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -8835,19 +9362,19 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.7619047619047619</v>
       </c>
     </row>
     <row r="9">
@@ -8863,23 +9390,23 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>1</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="10">
@@ -8895,51 +9422,55 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>初二 汇总</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>0.8888888888888888</v>
+      <c r="E11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="12">
@@ -8950,28 +9481,28 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.8095238095238095</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -8982,52 +9513,112 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
+          <t>初二 汇总</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6756756756756757</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>初中 汇总</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>0.8933333333333333</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0.5600000000000001</v>
+      <c r="C16" s="6" t="inlineStr"/>
+      <c r="D16" s="6" t="n">
+        <v>84</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.9166666666666666</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>0.6309523809523809</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688854287853916</t>
+          <t>1688854784881061</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854784881058</t>
+          <t>1688855639780332</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,17 +752,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -774,12 +774,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -791,12 +786,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -841,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -856,17 +851,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -878,12 +873,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -895,12 +885,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -945,32 +935,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688857790837398</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -989,17 +979,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1044,7 +1034,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688857115860438</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1054,22 +1044,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1093,12 +1083,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1143,32 +1133,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688857167940654</t>
+          <t>1688854497763413</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1180,29 +1170,24 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1247,7 +1232,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688854761929635</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1262,17 +1247,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1296,12 +1281,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1346,32 +1331,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1390,17 +1375,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1445,32 +1430,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688855270890446</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1482,29 +1467,24 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1549,32 +1529,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688857751871228</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1593,17 +1573,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1648,32 +1628,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688857167940654</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1685,24 +1665,29 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1747,7 +1732,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854894759300</t>
+          <t>1688855086834341</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1757,22 +1742,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1796,12 +1781,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1846,32 +1831,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688854281870550</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1890,17 +1875,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1945,32 +1930,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688856261784494</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1982,24 +1967,29 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2044,7 +2034,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688856920865401</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2059,17 +2049,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2081,11 +2071,11 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3333333333333333</v>
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2098,12 +2088,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2148,7 +2138,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688855270890512</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2158,22 +2148,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2197,12 +2187,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2247,7 +2237,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688854281870530</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2262,17 +2252,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2284,12 +2274,7 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>6,7,8,9</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
@@ -2301,12 +2286,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2351,7 +2336,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688854498774486</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2366,17 +2351,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2400,12 +2385,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2450,32 +2435,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688854784881054</t>
+          <t>1688855001729346,1688854706799328</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2490,21 +2475,26 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2549,7 +2539,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688857167940610</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2559,22 +2549,22 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2586,7 +2576,12 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
@@ -2598,12 +2593,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2648,7 +2643,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688854784881059</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2658,22 +2653,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2685,7 +2680,12 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -2697,12 +2697,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688854281870599</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2757,22 +2757,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2846,32 +2846,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2883,24 +2883,29 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2945,7 +2950,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2955,22 +2960,22 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2994,12 +2999,12 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3044,32 +3049,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3088,17 +3093,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3143,32 +3148,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688857790837332</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3192,17 +3197,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3247,32 +3252,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688855070755789</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3281,42 +3286,27 @@
         </is>
       </c>
       <c r="M28" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3361,7 +3351,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3371,22 +3361,22 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3410,12 +3400,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3460,32 +3450,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688855477810382</t>
+          <t>1688854476856492</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3497,24 +3487,34 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>20,21,22,23</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>18,19</t>
+        </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3559,32 +3559,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688854572834470</t>
+          <t>1688856995795370</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3603,17 +3603,17 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3658,32 +3658,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857167940610</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3695,11 +3695,11 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688855070755789</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3772,22 +3772,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688855593838985</t>
+          <t>1688858124858984</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688856475868784</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3970,22 +3970,22 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3997,12 +3997,7 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -4014,12 +4009,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4064,7 +4059,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688857790837033</t>
+          <t>1688857609868354</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4079,17 +4074,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4101,12 +4096,7 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -4118,12 +4108,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4168,32 +4158,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688855270890446</t>
+          <t>1688856311853482</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4205,24 +4195,29 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4267,7 +4262,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688854784881059</t>
+          <t>1688856819940740</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4277,22 +4272,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4304,12 +4299,7 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -4321,12 +4311,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4371,32 +4361,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688855001729346,1688854706799328</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4415,17 +4405,17 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4470,7 +4460,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688854476856492</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4480,22 +4470,22 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4519,12 +4509,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4569,7 +4559,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688857167940672</t>
+          <t>1688854575781532</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4584,17 +4574,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4606,15 +4596,15 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4623,12 +4613,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4673,32 +4663,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688854498774486</t>
+          <t>1688857167940672</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4710,24 +4700,29 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q42" t="n">
         <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4772,32 +4767,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688854281870530</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4816,17 +4811,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4871,32 +4866,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688855477810382</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4915,17 +4910,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4970,7 +4965,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4980,22 +4975,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5019,12 +5014,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5069,32 +5064,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857790837398</t>
+          <t>1688858289869798</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5113,17 +5108,17 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5168,32 +5163,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688854522754461</t>
+          <t>1688854784881054</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5205,11 +5200,11 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5217,17 +5212,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5272,32 +5267,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688856261784494</t>
+          <t>1688857167940637</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5321,17 +5316,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5376,32 +5371,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688857752769746</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5413,29 +5408,24 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5480,7 +5470,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688854522754143</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5495,17 +5485,17 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5529,12 +5519,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5579,7 +5569,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688856995795370</t>
+          <t>1688854287853876</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5589,22 +5579,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5616,7 +5606,12 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -5628,12 +5623,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5678,7 +5673,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688854784881061</t>
+          <t>1688854784881034</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5688,22 +5683,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5732,12 +5727,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5782,7 +5777,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5792,22 +5787,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5819,12 +5814,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -5836,12 +5826,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5886,7 +5876,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5896,22 +5886,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5920,13 +5910,28 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5935,12 +5940,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5985,32 +5990,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688858008853709</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6029,17 +6034,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6084,32 +6089,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688857452809589</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6121,29 +6126,24 @@
         <v>1</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q56" t="n">
         <v>1</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6198,22 +6198,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6287,32 +6287,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688855686929440</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6386,32 +6386,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688854572834470</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6423,29 +6423,24 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6490,32 +6485,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688856311853482</t>
+          <t>1688858275775684</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6527,29 +6522,24 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6594,32 +6584,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688857751871228</t>
+          <t>1688857790837332</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6631,24 +6621,29 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6708,7 +6703,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6792,7 +6787,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688855270890470</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6807,17 +6802,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6829,7 +6824,12 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
@@ -6841,12 +6841,12 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6891,32 +6891,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688854476856420</t>
+          <t>1688857452809516</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6935,17 +6935,17 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688858275775684</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7000,22 +7000,22 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7027,7 +7027,12 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -7039,12 +7044,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7089,7 +7094,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -7099,22 +7104,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7138,12 +7143,12 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7188,7 +7193,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688855292870141</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7203,17 +7208,17 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7225,12 +7230,7 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
@@ -7242,12 +7242,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7292,32 +7292,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7391,32 +7391,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688854497763413</t>
+          <t>1688854281870539</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7428,24 +7428,29 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7490,32 +7495,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688857167940637</t>
+          <t>1688855270890436</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7527,29 +7532,24 @@
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688856819940740</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -7604,22 +7604,22 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7631,7 +7631,12 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -7643,12 +7648,12 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7693,32 +7698,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7737,17 +7742,17 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7792,32 +7797,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688857452809516</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7836,17 +7841,17 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7891,32 +7896,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688858008853709</t>
+          <t>1688857790837033</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7928,24 +7933,29 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -7990,7 +8000,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688856261784534</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8005,17 +8015,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8027,15 +8037,15 @@
         <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q75" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -8044,12 +8054,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8094,7 +8104,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688854784881058</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -8109,17 +8119,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8131,7 +8141,12 @@
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
@@ -8143,12 +8158,12 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8208,7 +8223,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8297,32 +8312,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688855686929440</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8341,17 +8356,17 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8396,32 +8411,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688856261784534</t>
+          <t>1688857392814199</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8433,29 +8448,24 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8500,32 +8510,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688854784881034</t>
+          <t>1688854522754461</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8549,17 +8559,17 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8604,32 +8614,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688854575781532</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8644,26 +8654,21 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>17,18</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8764,10 +8769,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -8792,10 +8797,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -8824,10 +8829,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="5">
@@ -8850,16 +8855,16 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -8878,10 +8883,10 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="G6" t="n">
         <v>16</v>
@@ -8942,16 +8947,16 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -8980,10 +8985,10 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -9006,16 +9011,16 @@
         <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="11">
@@ -9040,10 +9045,10 @@
         <v>0.972972972972973</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="12">
@@ -9122,10 +9127,10 @@
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="G14" t="n">
         <v>53</v>
@@ -9161,7 +9166,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-10月8日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-10月9日</t>
         </is>
       </c>
     </row>
@@ -9251,10 +9256,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="5">
@@ -9279,10 +9284,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -9311,10 +9316,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="7">
@@ -9337,16 +9342,16 @@
         <v>10</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -9365,10 +9370,10 @@
         <v>21</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>16</v>
@@ -9429,16 +9434,16 @@
         <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -9467,10 +9472,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -9493,16 +9498,16 @@
         <v>8</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="13">
@@ -9527,10 +9532,10 @@
         <v>0.972972972972973</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6486486486486487</v>
       </c>
     </row>
     <row r="14">
@@ -9609,10 +9614,10 @@
         <v>84</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>53</v>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X81"/>
+  <dimension ref="A1:X87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688854784881061</t>
+          <t>1688857609868354</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -670,29 +670,24 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -737,32 +732,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688857790837398</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -781,17 +776,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -836,32 +831,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688854894759300</t>
+          <t>1688856261784494</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -873,24 +868,29 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857790837398</t>
+          <t>1688857167940672</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -972,7 +972,12 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -984,12 +989,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1044,22 +1049,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1083,12 +1088,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1133,32 +1138,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854497763413</t>
+          <t>1688854346851430</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1170,24 +1175,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1232,7 +1242,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688855270890512</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1242,22 +1252,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1281,12 +1291,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1331,32 +1341,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688854522754143</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1375,17 +1385,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1430,32 +1440,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688855270890446</t>
+          <t>1688857047921497</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1467,24 +1477,29 @@
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q10" t="n">
         <v>1</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1529,32 +1544,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688857751871228</t>
+          <t>1688854281870599</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1573,17 +1588,17 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1628,32 +1643,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688857167940654</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1665,29 +1680,29 @@
         <v>1</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1732,32 +1747,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688854522754461</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1769,24 +1784,29 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1831,32 +1851,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688854281870539</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1868,24 +1888,29 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1930,32 +1955,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688856261784494</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1979,17 +2004,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2034,32 +2059,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688854287853916</t>
+          <t>1688855051855742</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2083,17 +2108,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2138,7 +2163,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2148,22 +2173,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2187,12 +2212,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2237,32 +2262,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688854281870530</t>
+          <t>1688858289869798</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2281,17 +2306,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2336,32 +2361,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854498774486</t>
+          <t>1688855051855847</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2373,24 +2398,29 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2435,32 +2465,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688855001729346,1688854706799328</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2475,26 +2505,21 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2539,32 +2564,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688857167940610</t>
+          <t>1688854572834470</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2576,29 +2601,24 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2643,7 +2663,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688854784881059</t>
+          <t>1688854894759481</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2653,22 +2673,22 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2680,12 +2700,7 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
@@ -2697,12 +2712,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2747,7 +2762,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688857790837332</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2757,22 +2772,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2784,7 +2799,12 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
@@ -2796,12 +2816,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2846,7 +2866,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2856,22 +2876,22 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2883,12 +2903,7 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
@@ -2900,12 +2915,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2950,32 +2965,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688854281870530</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2994,17 +3009,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3049,32 +3064,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688857392814199</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3093,17 +3108,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3148,32 +3163,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688857047921523</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3197,17 +3212,17 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3252,7 +3267,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688854497763413</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3262,22 +3277,22 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3301,12 +3316,12 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3351,32 +3366,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3395,17 +3410,17 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3450,32 +3465,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688854476856492</t>
+          <t>1688854784881034</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3487,34 +3502,29 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3559,32 +3569,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688856995795370</t>
+          <t>1688855477810382</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3603,17 +3613,17 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3658,32 +3668,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688855292870141</t>
+          <t>1688857167940654</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3695,11 +3705,11 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -3707,17 +3717,17 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3762,7 +3772,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688855070755789</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3772,22 +3782,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3811,12 +3821,12 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3861,32 +3871,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688854476856492</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3898,24 +3908,29 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3960,32 +3975,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4004,17 +4019,17 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4059,7 +4074,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688854575781532</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4074,17 +4089,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4108,12 +4123,12 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>崔红月</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>cuihongyue</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4158,32 +4173,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688856311853482</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4195,29 +4210,24 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4262,7 +4272,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688856819940740</t>
+          <t>1688854784881061</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4277,17 +4287,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4299,7 +4309,12 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -4311,12 +4326,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4361,7 +4376,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4371,22 +4386,22 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4410,12 +4425,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4460,7 +4475,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688857751871228</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4475,17 +4490,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4509,12 +4524,12 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4559,32 +4574,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688854575781532</t>
+          <t>1688854287853876</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4596,29 +4611,29 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4663,32 +4678,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688857167940672</t>
+          <t>1688855270890470</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4712,17 +4727,17 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4767,32 +4782,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688855086834341</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4811,17 +4826,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4866,32 +4881,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688855477810382</t>
+          <t>1688857452809516</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4910,17 +4925,17 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4965,32 +4980,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688856261784534</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5002,24 +5017,29 @@
         <v>1</v>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q45" t="n">
         <v>1</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5064,32 +5084,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688858124858984</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5108,17 +5128,17 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5163,32 +5183,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688854784881054</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5200,11 +5220,11 @@
         <v>1</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -5212,17 +5232,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5267,32 +5287,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688857167940637</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5316,17 +5336,17 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5371,32 +5391,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5415,17 +5435,17 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5470,7 +5490,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688856819940740</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5480,22 +5500,22 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5519,12 +5539,12 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5569,7 +5589,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688858275775684</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5579,22 +5599,22 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5606,12 +5626,7 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -5623,12 +5638,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5673,7 +5688,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688854784881034</t>
+          <t>1688857167940610</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5683,22 +5698,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5727,12 +5742,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5777,32 +5792,32 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688854784881058</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5814,24 +5829,29 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5876,7 +5896,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688856475868784</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5886,22 +5906,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5910,28 +5930,13 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5940,12 +5945,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5990,7 +5995,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688858008853709</t>
+          <t>1688855270890436</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6005,17 +6010,17 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6027,7 +6032,12 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
@@ -6039,12 +6049,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6089,32 +6099,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6133,17 +6143,17 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6188,7 +6198,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688854784881059</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6198,22 +6208,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6225,7 +6235,12 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
@@ -6237,12 +6252,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6287,7 +6302,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688855686929440</t>
+          <t>1688856995795370</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6302,17 +6317,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6336,12 +6351,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6386,32 +6401,32 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688854572834470</t>
+          <t>1688855639780332</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6430,17 +6445,17 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6485,7 +6500,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688858275775684</t>
+          <t>1688855070755789</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6495,22 +6510,22 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6525,7 +6540,12 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6534,12 +6554,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6584,32 +6604,32 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688857790837332</t>
+          <t>1688855270890446</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6621,29 +6641,24 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>谷晨旭</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>guchenxu</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6688,7 +6703,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688854894759481</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6698,22 +6713,22 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6728,7 +6743,12 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6737,12 +6757,12 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6787,32 +6807,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688857047921476</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6836,17 +6856,17 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6891,32 +6911,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688857452809516</t>
+          <t>1688857167940637</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6928,24 +6948,29 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6990,32 +7015,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7027,29 +7052,24 @@
         <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7094,32 +7114,32 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7138,17 +7158,17 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7193,7 +7213,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688856920865401</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -7203,22 +7223,22 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7242,12 +7262,12 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7292,32 +7312,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7336,17 +7356,17 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7391,32 +7411,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688854498774486</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7428,29 +7448,24 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7495,32 +7510,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688857115860438</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7539,17 +7554,17 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7594,32 +7609,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7631,11 +7646,11 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6,7</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -7643,17 +7658,17 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7698,32 +7713,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7735,24 +7750,29 @@
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7797,32 +7817,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688855593838985</t>
+          <t>1688854784881054</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7834,24 +7854,29 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>0.2222222222222222</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
+        </is>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7896,32 +7921,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688857790837033</t>
+          <t>1688854281870550</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7933,11 +7958,11 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,11,12</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -7945,17 +7970,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8000,7 +8025,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688856261784534</t>
+          <t>1688857790837033</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -8015,17 +8040,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8034,7 +8059,12 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -8045,7 +8075,12 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -8054,12 +8089,12 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8104,32 +8139,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688854784881058</t>
+          <t>1688858008853709</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8141,29 +8176,24 @@
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8208,32 +8238,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688854346851430</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8245,29 +8275,24 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8312,32 +8337,32 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688857460767926</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8349,24 +8374,29 @@
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q78" t="n">
         <v>1</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8411,32 +8441,32 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8448,24 +8478,29 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8510,32 +8545,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688854522754461</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8547,29 +8582,24 @@
         <v>1</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8614,32 +8644,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688854476856420</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8658,17 +8688,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8682,6 +8712,620 @@
         </is>
       </c>
       <c r="X81" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1688854706799328,1688855001729346</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>王星晨</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>wangxingchen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1688854761929635</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>张亦浩</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>zhangyihao</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>1</v>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>张亦浩</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>zhangyihao</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1688857752769746</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>张嘉轩</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>zhangjiaxuan</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>张嘉轩</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>zhangjiaxuan</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1688857452809589</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>1</v>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1688855686929440</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>10,11,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>杨志杰</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>yangzhijie01</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>20261009</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1688856311853482</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>徐源</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>xuyuan01</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>徐源</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>xuyuan01</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -8769,10 +9413,10 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="3">
@@ -8797,10 +9441,10 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -8855,16 +9499,16 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -8883,16 +9527,16 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9523809523809523</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="7">
@@ -8921,10 +9565,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="8">
@@ -8947,10 +9591,10 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G8" t="n">
         <v>6</v>
@@ -9017,10 +9661,10 @@
         <v>0.875</v>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H10" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="11">
@@ -9039,16 +9683,16 @@
         <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
-        <v>0.972972972972973</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="G11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6486486486486487</v>
+        <v>0.6756756756756757</v>
       </c>
     </row>
     <row r="12">
@@ -9068,19 +9712,19 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="n">
         <v>16</v>
       </c>
-      <c r="E12" t="n">
-        <v>10</v>
-      </c>
       <c r="F12" t="n">
-        <v>0.625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G12" t="n">
         <v>4</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="13">
@@ -9096,19 +9740,19 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
+        <v>18</v>
+      </c>
+      <c r="E13" t="n">
         <v>16</v>
       </c>
-      <c r="E13" t="n">
-        <v>10</v>
-      </c>
       <c r="F13" t="n">
-        <v>0.625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="14">
@@ -9124,19 +9768,19 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E14" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9418604651162791</v>
       </c>
       <c r="G14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5930232558139535</v>
       </c>
     </row>
   </sheetData>
@@ -9166,7 +9810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-10月9日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-10月11日</t>
         </is>
       </c>
     </row>
@@ -9256,10 +9900,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -9284,10 +9928,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -9342,16 +9986,16 @@
         <v>10</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -9370,16 +10014,16 @@
         <v>21</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.9523809523809523</v>
+        <v>1</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="9">
@@ -9408,10 +10052,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
     </row>
     <row r="10">
@@ -9434,10 +10078,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>6</v>
@@ -9504,10 +10148,10 @@
         <v>0.875</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="13">
@@ -9526,16 +10170,16 @@
         <v>37</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.972972972972973</v>
+        <v>0.918918918918919</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.6486486486486487</v>
+        <v>0.6756756756756757</v>
       </c>
     </row>
     <row r="14">
@@ -9555,19 +10199,19 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="E14" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="F14" s="5" t="n">
-        <v>0.625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>4</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="15">
@@ -9583,19 +10227,19 @@
       </c>
       <c r="C15" s="6" t="inlineStr"/>
       <c r="D15" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E15" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>10</v>
-      </c>
       <c r="F15" s="7" t="n">
-        <v>0.625</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>4</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.25</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="16">
@@ -9611,19 +10255,19 @@
       </c>
       <c r="C16" s="6" t="inlineStr"/>
       <c r="D16" s="6" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9418604651162791</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.6309523809523809</v>
+        <v>0.5930232558139535</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X87"/>
+  <dimension ref="A1:X109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -670,24 +670,29 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -708,7 +713,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -732,32 +737,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688857790837398</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -776,17 +781,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -807,7 +812,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -831,32 +836,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688856261784494</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -868,29 +873,24 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -911,7 +911,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -935,32 +935,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857167940672</t>
+          <t>1688856819940740</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -972,29 +972,24 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1015,7 +1010,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1039,32 +1034,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688854894759300</t>
+          <t>1688856454985963</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>李秉彰</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>libingzhang</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1076,24 +1071,29 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>李秉彰</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>libingzhang</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1114,7 +1114,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854346851430</t>
+          <t>1688857609868354</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1148,22 +1148,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>新兵营彬</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1175,15 +1175,15 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1218,7 +1218,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1242,32 +1242,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1341,32 +1341,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1416,7 +1416,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1440,32 +1440,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688857047921497</t>
+          <t>1688855686929440</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>纪覃思</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>jitansi</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1474,7 +1474,12 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>21,22,23</t>
+        </is>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1485,21 +1490,26 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>21,22,23</t>
+        </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>纪覃思</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>jitansi</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1520,7 +1530,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1544,32 +1554,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688855051855742</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1578,27 +1588,42 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1619,7 +1644,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1643,7 +1668,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1658,17 +1683,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1683,12 +1708,7 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1697,12 +1717,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1723,7 +1743,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1747,32 +1767,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854522754461</t>
+          <t>1688854784881061</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1796,17 +1816,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>贾美宝</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>jiameibao</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1827,7 +1847,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1851,7 +1871,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688855960978536</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1866,17 +1886,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>李志辉</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>lizhihui03</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1905,12 +1925,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>李志辉</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>lizhihui03</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1931,7 +1951,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1955,32 +1975,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688856454986646</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>陈仪薇</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>chenyiwei</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2000,21 +2020,26 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>陈仪薇</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>chenyiwei</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2035,7 +2060,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2059,32 +2084,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688855051855742</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>武金贤</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>wujinxian</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2096,29 +2121,24 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>武金贤</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>wujinxian</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2139,7 +2159,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2163,7 +2183,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688857167940637</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2173,22 +2193,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2197,13 +2217,28 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2212,12 +2247,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2238,7 +2273,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2262,32 +2297,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688856261784534</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营彬</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2299,24 +2334,29 @@
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q18" t="n">
         <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2337,7 +2377,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2361,32 +2401,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688855051855847</t>
+          <t>1688857167940610</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>王安冉</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>wanganran</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2410,17 +2450,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>王安冉</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>wanganran</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2441,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2465,7 +2505,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688854476856492</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2475,22 +2515,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2502,7 +2542,12 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
@@ -2514,12 +2559,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>张一卓</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>zhangyizhuo01</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2540,7 +2585,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2564,7 +2609,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688854572834470</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2579,17 +2624,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2613,12 +2658,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2639,7 +2684,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2663,7 +2708,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688854894759481</t>
+          <t>1688856995795370</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2678,17 +2723,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2712,12 +2757,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2738,7 +2783,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2762,32 +2807,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688857790837332</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2799,29 +2844,24 @@
         <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>1</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2842,7 +2882,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2866,32 +2906,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688856454986008</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>杜冠臻</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>duguanzhen</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2903,24 +2943,29 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>杜冠臻</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>duguanzhen</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2941,7 +2986,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2965,32 +3010,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688854281870530</t>
+          <t>1688856311853482</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3002,24 +3047,29 @@
         <v>1</v>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q25" t="n">
         <v>1</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3040,7 +3090,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3064,32 +3114,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688857452809516</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3108,17 +3158,17 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3139,7 +3189,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3163,32 +3213,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688857047921523</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>王姿</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>wangzi</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3197,32 +3247,42 @@
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>王姿</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>wangzi</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3243,7 +3303,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3267,32 +3327,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688854497763413</t>
+          <t>1688854761929635</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3304,24 +3364,29 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>9,10,11</t>
+        </is>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3342,7 +3407,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3366,7 +3431,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688855070755789</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3381,17 +3446,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3415,12 +3480,12 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3441,7 +3506,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3465,32 +3530,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688854784881034</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3502,11 +3567,11 @@
         <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -3514,17 +3579,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3545,7 +3610,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3569,32 +3634,32 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688855477810382</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3606,24 +3671,29 @@
         <v>1</v>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q31" t="n">
         <v>1</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3644,7 +3714,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3668,32 +3738,32 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857167940654</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3705,29 +3775,24 @@
         <v>1</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>野艳红</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>yeyanhong</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3748,7 +3813,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3772,32 +3837,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3809,24 +3874,29 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3847,7 +3917,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3871,32 +3941,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688854476856492</t>
+          <t>1688855270890512</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3908,29 +3978,24 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>张一卓</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>zhangyizhuo01</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3951,7 +4016,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3975,32 +4040,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688856920865401</t>
+          <t>1688854815837469</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4012,24 +4077,29 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4050,7 +4120,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4074,32 +4144,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688854575781532</t>
+          <t>1688854498774486</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4118,17 +4188,17 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>崔红月</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>cuihongyue</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4149,7 +4219,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4173,7 +4243,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688855593838985</t>
+          <t>1688855477810382</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4188,17 +4258,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4222,12 +4292,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4248,7 +4318,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4272,32 +4342,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688854784881061</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4309,29 +4379,24 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4352,7 +4417,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4376,32 +4441,32 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688857460767926</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4413,24 +4478,29 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q39" t="n">
         <v>1</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4451,7 +4521,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4475,32 +4545,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688857751871228</t>
+          <t>1688854706799328,1688855001729346</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4519,17 +4589,17 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4550,7 +4620,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4574,7 +4644,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688857790837332</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4589,17 +4659,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4611,11 +4681,11 @@
         <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -4628,12 +4698,12 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4654,7 +4724,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4678,32 +4748,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688856454986038</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>范佳敏</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>fanjiamin</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4715,11 +4785,11 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -4727,17 +4797,17 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>范佳敏</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>fanjiamin</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4758,7 +4828,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4782,7 +4852,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688854894759558</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4792,22 +4862,22 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4831,12 +4901,12 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4857,7 +4927,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4881,32 +4951,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688857452809516</t>
+          <t>1688857047921523</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4918,24 +4988,29 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q44" t="n">
         <v>1</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4956,7 +5031,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4980,7 +5055,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688856261784534</t>
+          <t>1688856454985952</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4995,17 +5070,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>赵权亮</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhaoquanliang</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5014,7 +5089,12 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -5025,7 +5105,12 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -5034,12 +5119,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>赵权亮</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhaoquanliang</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5060,7 +5145,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -5084,32 +5169,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688856454985976</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张倩希</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangqianxi</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5118,27 +5203,42 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,22,23</t>
+        </is>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,22,23</t>
+        </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>张倩希</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhangqianxi</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5159,7 +5259,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5183,32 +5283,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688856454985988</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>白肖阳</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>baixiaoyang</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5232,17 +5332,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>白肖阳</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>baixiaoyang</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5263,7 +5363,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5287,7 +5387,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688854287853916</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5297,22 +5397,22 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5324,12 +5424,7 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
@@ -5341,12 +5436,12 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5367,7 +5462,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5391,32 +5486,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688854476856420</t>
+          <t>1688854281870539</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5428,24 +5523,29 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q49" t="n">
         <v>1</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5466,7 +5566,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5490,32 +5590,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688856819940740</t>
+          <t>1688856454986017</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>周涛</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>zhoutao</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5527,24 +5627,29 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>周涛</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>zhoutao</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5565,7 +5670,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5589,7 +5694,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688858275775684</t>
+          <t>1688855639780332</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5604,17 +5709,17 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5638,12 +5743,12 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5664,7 +5769,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5688,7 +5793,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688857167940610</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5698,22 +5803,22 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5725,15 +5830,15 @@
         <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5742,12 +5847,12 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5768,7 +5873,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5792,7 +5897,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688854784881058</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5802,22 +5907,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5829,12 +5934,7 @@
         <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -5846,12 +5946,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5872,7 +5972,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5896,7 +5996,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688854784881054</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5911,17 +6011,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5933,7 +6033,12 @@
         <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
@@ -5945,12 +6050,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -5971,7 +6076,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5995,32 +6100,32 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6032,11 +6137,11 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>17,18,19,20,21,22,23</t>
+          <t>8,9,10,12</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -6044,17 +6149,17 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6075,7 +6180,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -6099,32 +6204,32 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688854603884803</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6143,17 +6248,17 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6174,7 +6279,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6198,7 +6303,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688854784881059</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6208,22 +6313,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6235,12 +6340,7 @@
         <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
         <v>1</v>
@@ -6252,12 +6352,12 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6278,7 +6378,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6302,7 +6402,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688856995795370</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6312,22 +6412,22 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6339,7 +6439,12 @@
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
@@ -6351,12 +6456,12 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6377,7 +6482,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6401,7 +6506,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688854894759430</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6411,22 +6516,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6441,7 +6546,12 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -6450,12 +6560,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6476,7 +6586,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6500,32 +6610,32 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688855070755789</t>
+          <t>1688856454986129</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>liwenchao</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6534,32 +6644,42 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q60" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>liwenchao</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6580,7 +6700,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6604,7 +6724,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688855270890446</t>
+          <t>1688854522754461</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6614,22 +6734,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6641,7 +6761,12 @@
         <v>1</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q61" t="n">
         <v>1</v>
@@ -6653,12 +6778,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>谷晨旭</t>
+          <t>贾美宝</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>guchenxu</t>
+          <t>jiameibao</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6679,7 +6804,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6703,32 +6828,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688854281870530</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6743,26 +6868,21 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6783,7 +6903,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6807,32 +6927,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688857047921476</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>单昊天</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>shanhaotian</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6844,29 +6964,24 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>单昊天</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>shanhaotian</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6887,7 +7002,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6911,32 +7026,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688857167940637</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6948,11 +7063,11 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -6960,17 +7075,17 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -6991,7 +7106,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7015,32 +7130,32 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688857372708211</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7059,17 +7174,17 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7090,7 +7205,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -7114,32 +7229,32 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688857167940654</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营彬</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7151,24 +7266,29 @@
         <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q66" t="n">
         <v>1</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7189,7 +7309,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7213,32 +7333,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688854784881034</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7250,24 +7370,29 @@
         <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q67" t="n">
         <v>1</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7288,7 +7413,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7312,7 +7437,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688857145762192</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7322,22 +7447,22 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7361,12 +7486,12 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7387,7 +7512,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7411,32 +7536,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688854498774486</t>
+          <t>1688854346851430</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营彬</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7448,24 +7573,29 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7486,7 +7616,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7510,32 +7640,32 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688856261784494</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营彬</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7547,24 +7677,29 @@
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7585,7 +7720,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7609,32 +7744,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688855292870141</t>
+          <t>1688857047921497</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7646,11 +7781,11 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>6,7</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -7658,17 +7793,17 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>纪覃思</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>jitansi</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7689,7 +7824,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7713,7 +7848,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7723,22 +7858,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7767,12 +7902,12 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7793,7 +7928,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7817,7 +7952,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688854784881054</t>
+          <t>1688854784881036</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7827,22 +7962,22 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7854,12 +7989,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q73" t="n">
         <v>1</v>
@@ -7871,12 +8001,12 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -7897,7 +8027,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -7921,32 +8051,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>初阶一</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7958,29 +8088,29 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>6,7,8,9,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>初一</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8001,7 +8131,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -8025,32 +8155,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688857790837033</t>
+          <t>1688856475868784</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8059,42 +8189,27 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8115,7 +8230,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -8154,7 +8269,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8214,7 +8329,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -8238,32 +8353,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688856644818249</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8275,24 +8390,29 @@
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="Q77" t="n">
         <v>1</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8313,7 +8433,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -8337,7 +8457,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688857460767926</t>
+          <t>1688855051855847</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8352,17 +8472,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>季子傲</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>jiziao</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8391,12 +8511,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>季子傲</t>
+          <t>王安冉</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>jiziao</t>
+          <t>wanganran</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8417,7 +8537,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -8441,7 +8561,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688857703847806</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -8456,17 +8576,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -8478,12 +8598,7 @@
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
         <v>1</v>
@@ -8495,12 +8610,12 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -8521,7 +8636,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -8545,32 +8660,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688854522754143</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8589,17 +8704,17 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8620,7 +8735,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -8644,32 +8759,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688858275775684</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>初阶三</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8688,17 +8803,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>初三</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8719,7 +8834,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -8743,32 +8858,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688854706799328,1688855001729346</t>
+          <t>1688854784881059</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶二</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8780,24 +8895,29 @@
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初二</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8818,7 +8938,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -8842,32 +8962,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8886,17 +9006,17 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -8917,7 +9037,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -8941,7 +9061,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688857115860438</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8956,17 +9076,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -8990,12 +9110,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -9016,7 +9136,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -9040,32 +9160,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688856454986057</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>马元帅</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>mayuanshuai</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9077,24 +9197,34 @@
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15</t>
+        </is>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>21,23</t>
+        </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>马元帅</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>mayuanshuai</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -9115,7 +9245,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -9139,32 +9269,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688855686929440</t>
+          <t>1688857167940616</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>初阶二</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>蔺宏业</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>linhongye</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9173,32 +9303,42 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O86" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>10,11,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>初二</t>
+          <t>初一</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>蔺宏业</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>linhongye</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9219,7 +9359,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20261009</v>
+        <v>20261016</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -9243,32 +9383,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688856311853482</t>
+          <t>1688854776688740</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>初阶一</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9285,11 +9425,11 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -9302,30 +9442,2268 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>张泽栋</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>zhangzedong</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1688857452809589</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>张硕研</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>zhangshuoyan</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1688854287853876</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>董宇波</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>dongyubo</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>董宇波</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>dongyubo</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1688855270890470</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>靳琪琪</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>jinqiqi</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>靳琪琪</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>jinqiqi</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1688854281870550</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>王紫东</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>wangzidong</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>1</v>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>王紫东</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>wangzidong</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1688857751871228</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>汪光磊</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>wangguanglei</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>汪光磊</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>wangguanglei</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1688854572834470</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>重装九组</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>张浩</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>zhanghao06</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1688858289869798</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>1</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>冯一帆</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>fengyifan01</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1688854470818602</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>孙宇哲</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>sunyuzhe</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>孙宇哲</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>sunyuzhe</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1688854497763413</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>初阶三</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>天天向上</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>姜傲爽</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>jiangaoshuang</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>1</v>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>初三</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>姜傲爽</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>jiangaoshuang</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1688857392814199</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>申谭谭</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>shentantan</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>1</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>申谭谭</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>shentantan</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1688857790837398</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
           <t>新兵营</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>徐源</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>xuyuan01</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>新兵营彬</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>马浩楠</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>mahaonan01</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>1</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>马浩楠</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>mahaonan01</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1688857047921476</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>单昊天</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>shanhaotian</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>1</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>单昊天</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>shanhaotian</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1688854894759481</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>张宝华</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>zhangbaohua01</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
+      <c r="O100" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>1</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>张宝华</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>zhangbaohua01</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1688857790837033</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>新兵营彬</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>张心驰</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>zhangxinchi</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1688858124858984</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>1</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>1</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>安怡宣</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>anyixuan</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1688857167940672</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>新兵营彬</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>王璐</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>wanglu03</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>1</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>1</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>王璐</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>wanglu03</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1688854281870599</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>秦思雨</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>qinsiyu01</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>1</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>秦思雨</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>qinsiyu01</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1688854706800124</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>云程发轫</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>杨文昭</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>yangwenzhao</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>杨文昭</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>yangwenzhao</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1688857752769746</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>张嘉轩</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>zhangjiaxuan</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>1</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>张嘉轩</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>zhangjiaxuan</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1688854784881058</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>翟林志</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>zhailinzhi</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>1</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>翟林志</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>zhailinzhi</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1688855086834341</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>初阶二</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>超级莱米</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>魏晨阳</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>weichenyang</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>1</v>
+      </c>
+      <c r="O108" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>初二</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>魏晨阳</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>weichenyang</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>石家庄初短</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>20261016</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>初阶</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1688855270890436</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>初阶一</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>重装五组</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>张学伦</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>zhangxuelun01</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M109" t="n">
+        <v>1</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>1</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>初一</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>张学伦</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>zhangxuelun01</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -9342,7 +11720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9404,19 +11782,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="3">
@@ -9432,19 +11810,19 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="4">
@@ -9464,19 +11842,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G4" t="n">
         <v>7</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="5">
@@ -9524,19 +11902,19 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>21</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="G6" t="n">
         <v>15</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="7">
@@ -9559,10 +11937,10 @@
         <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G7" t="n">
         <v>9</v>
@@ -9588,19 +11966,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="9">
@@ -9623,16 +12001,16 @@
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="10">
@@ -9652,19 +12030,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -9680,19 +12058,19 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F11" t="n">
-        <v>0.918918918918919</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6818181818181818</v>
       </c>
     </row>
     <row r="12">
@@ -9712,19 +12090,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="13">
@@ -9735,24 +12113,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>新兵营彬</t>
+        </is>
+      </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.75</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="14">
@@ -9763,24 +12145,52 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9418604651162791</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="G14" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5930232558139535</v>
+        <v>0.06896551724137931</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>109</v>
+      </c>
+      <c r="E15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.8348623853211009</v>
+      </c>
+      <c r="G15" t="n">
+        <v>54</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4954128440366973</v>
       </c>
     </row>
   </sheetData>
@@ -9794,7 +12204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -9810,7 +12220,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-10月11日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-10月14日</t>
         </is>
       </c>
     </row>
@@ -9891,19 +12301,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.7</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="5">
@@ -9919,19 +12329,19 @@
       </c>
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>7</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>0.7</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="6">
@@ -9951,19 +12361,19 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="G6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="7">
@@ -10011,19 +12421,19 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>21</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0.9130434782608695</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>15</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6521739130434783</v>
       </c>
     </row>
     <row r="9">
@@ -10046,10 +12456,10 @@
         <v>14</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="G9" s="4" t="n">
         <v>9</v>
@@ -10075,19 +12485,19 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="11">
@@ -10110,16 +12520,16 @@
         <v>9</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="12">
@@ -10139,19 +12549,19 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -10167,19 +12577,19 @@
       </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.918918918918919</v>
+        <v>0.8863636363636364</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.6818181818181818</v>
       </c>
     </row>
     <row r="14">
@@ -10199,47 +12609,51 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>新兵营 汇总</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="G15" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0.2222222222222222</v>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>新兵营彬</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.125</v>
       </c>
     </row>
     <row r="16">
@@ -10250,24 +12664,52 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>初中 汇总</t>
+          <t>新兵营 汇总</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr"/>
       <c r="D16" s="6" t="n">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0.9418604651162791</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.5930232558139535</v>
+        <v>0.06896551724137931</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>初中 汇总</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr"/>
+      <c r="D17" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>0.8348623853211009</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>0.4954128440366973</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/石家庄初短/石家庄-石家庄初短-销售风灵在线率明细数据.xlsx
@@ -482,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X110"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,32 +633,32 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688854346851430</t>
+          <t>1688854522753923</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -670,29 +670,24 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>吕晓菲</t>
+          <t>刘莹凤</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>lvxiaofei</t>
+          <t>liuyingfeng</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -737,32 +732,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688855928851644</t>
+          <t>1688855270890470</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -774,24 +769,29 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>杨璐</t>
+          <t>靳琪琪</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>yanglu</t>
+          <t>jinqiqi</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -836,32 +836,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688856454986038</t>
+          <t>1688857145762192</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>范佳敏</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>fanjiamin</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -873,29 +873,24 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>范佳敏</t>
+          <t>张旭青</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>fanjiamin</t>
+          <t>zhangxuqing</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -940,32 +935,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857460767926</t>
+          <t>1688854281870599</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>季子傲</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>jiziao</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -974,42 +969,27 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>季子傲</t>
+          <t>秦思雨</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>jiziao</t>
+          <t>qinsiyu01</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1054,32 +1034,32 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688856920865401</t>
+          <t>1688854894759481</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1091,29 +1071,24 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>13,19,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>刘晓松</t>
+          <t>张宝华</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>liuxiaosong</t>
+          <t>zhangbaohua01</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1158,32 +1133,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854522754361</t>
+          <t>1688854784881061</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1195,24 +1170,29 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>张鑫禹</t>
+          <t>闫慧清</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>zhangxinyu01</t>
+          <t>yanhuiqing</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1257,32 +1237,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688858008853709</t>
+          <t>1688856454986038</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>范佳敏</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>fanjiamin</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1294,11 +1274,11 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>11,12,13</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1306,17 +1286,17 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>耿亚轩</t>
+          <t>范佳敏</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>gengyaxuan</t>
+          <t>fanjiamin</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1361,32 +1341,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688857452809516</t>
+          <t>1688856475868784</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1398,29 +1378,24 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>郭雅静</t>
+          <t>胡洋铭</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>guoyajing</t>
+          <t>huyangming</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1465,32 +1440,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688855001729346,1688854706799328</t>
+          <t>1688856624782683</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1509,17 +1484,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>王星晨</t>
+          <t>张硕辉</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>wangxingchen</t>
+          <t>zhangshuohui01</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1564,7 +1539,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688857605746717</t>
+          <t>1688855593838985</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1574,22 +1549,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1601,12 +1576,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1618,12 +1588,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>郭甜甜</t>
+          <t>彭涛</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>guotiantian</t>
+          <t>pengtao</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1668,32 +1638,32 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688857047921476</t>
+          <t>1688857167940672</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>单昊天</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>shanhaotian</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1702,12 +1672,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1718,26 +1683,21 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>7,8,9,10,11,12,13,14,15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>单昊天</t>
+          <t>王璐</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>shanhaotian</t>
+          <t>wanglu03</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1782,32 +1742,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854281870569</t>
+          <t>1688854497763413</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1819,29 +1779,24 @@
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>李洋</t>
+          <t>姜傲爽</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>liyang06</t>
+          <t>jiangaoshuang</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1886,32 +1841,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688857254754511</t>
+          <t>1688856819940740</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1930,17 +1885,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>李旭东</t>
+          <t>芦凯</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>lixudong</t>
+          <t>lukai</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1985,32 +1940,32 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688857167940672</t>
+          <t>1688857452809516</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2022,29 +1977,24 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>王璐</t>
+          <t>郭雅静</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>wanglu03</t>
+          <t>guoyajing</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2089,32 +2039,32 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688854260743321</t>
+          <t>1688857047921476</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2126,11 +2076,11 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9444444444444444</v>
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2138,17 +2088,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>杨鹏飞</t>
+          <t>单昊天</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>yangpengfei</t>
+          <t>shanhaotian</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2193,32 +2143,32 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688855270890470</t>
+          <t>1688858199721276</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2230,29 +2180,24 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>靳琪琪</t>
+          <t>赵静静</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>jinqiqi</t>
+          <t>zhaojingjing</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2297,7 +2242,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688854498774486</t>
+          <t>1688855270890512</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2312,17 +2257,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2337,11 +2282,11 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2351,12 +2296,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>高梓慧</t>
+          <t>浦岩岩</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>gaozihui</t>
+          <t>puyanyan</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2401,7 +2346,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854784881058</t>
+          <t>1688857047921523</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2416,17 +2361,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2438,11 +2383,11 @@
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2455,12 +2400,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>翟林志</t>
+          <t>王姿</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>zhailinzhi</t>
+          <t>wangzi</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2505,32 +2450,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688855070755789</t>
+          <t>1688856454986017</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>周涛</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhoutao</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2542,11 +2487,11 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16,17</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2554,17 +2499,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>严绍源</t>
+          <t>周涛</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>yanshaoyuan</t>
+          <t>zhoutao</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2609,32 +2554,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1688856644818249</t>
+          <t>1688854706799328,1688855001729346</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2649,26 +2594,21 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>6,7,13,14,15,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>郭少华</t>
+          <t>王星晨</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>guoshaohua</t>
+          <t>wangxingchen</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2713,32 +2653,32 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1688854287853876</t>
+          <t>1688855292870141</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2750,24 +2690,29 @@
         <v>1</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q22" t="n">
         <v>1</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>董宇波</t>
+          <t>赵世文</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>dongyubo</t>
+          <t>zhaoshiwen</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2812,7 +2757,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1688854522753923</t>
+          <t>1688854706800124</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2822,22 +2767,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2861,12 +2806,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>刘莹凤</t>
+          <t>杨文昭</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>liuyingfeng</t>
+          <t>yangwenzhao</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2911,32 +2856,32 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1688854476856420</t>
+          <t>1688856454985976</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张倩希</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangqianxi</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2948,24 +2893,29 @@
         <v>1</v>
       </c>
       <c r="O24" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>李雨薇</t>
+          <t>张倩希</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>liyuwei</t>
+          <t>zhangqianxi</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3010,32 +2960,32 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1688854784881061</t>
+          <t>1688856454985988</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>白肖阳</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>baixiaoyang</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3059,17 +3009,17 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>闫慧清</t>
+          <t>白肖阳</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>yanhuiqing</t>
+          <t>baixiaoyang</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3114,32 +3064,32 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1688856624782683</t>
+          <t>1688854522754361</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3151,29 +3101,24 @@
         <v>1</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
         <v>1</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>张硕辉</t>
+          <t>张鑫禹</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>zhangshuohui01</t>
+          <t>zhangxinyu01</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3218,32 +3163,32 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1688855960978536</t>
+          <t>1688855477810382</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>李志辉</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>lizhihui03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3255,29 +3200,24 @@
         <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>李志辉</t>
+          <t>李奕昕</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>lizhihui03</t>
+          <t>liyixin</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3322,32 +3262,32 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1688856261784494</t>
+          <t>1688855270890491</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3359,29 +3299,24 @@
         <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
         <v>1</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>孟思楠</t>
+          <t>郭佳浩</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>mengsinan</t>
+          <t>guojiahao</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3426,32 +3361,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1688855770825630</t>
+          <t>1688854281870569</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3463,24 +3398,29 @@
         <v>1</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>高佳华</t>
+          <t>李洋</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>gaojiahua</t>
+          <t>liyang06</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3525,32 +3465,32 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1688854497763413</t>
+          <t>1688855770825630</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3569,17 +3509,17 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>姜傲爽</t>
+          <t>高佳华</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>jiangaoshuang</t>
+          <t>gaojiahua</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3624,7 +3564,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1688858124858856</t>
+          <t>1688854894759558</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3634,22 +3574,22 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3673,12 +3613,12 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>王佳琦</t>
+          <t>胡茹茹</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>wangjiaqi05</t>
+          <t>hururu</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3723,7 +3663,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1688857372708211</t>
+          <t>1688854281870530</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3733,22 +3673,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3772,12 +3712,12 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>崔玉婷</t>
+          <t>赵小漫</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>cuiyuting</t>
+          <t>zhaoxiaoman</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3822,32 +3762,32 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1688856454986017</t>
+          <t>1688854815837469</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>周涛</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>zhoutao</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3859,29 +3799,24 @@
         <v>1</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>周涛</t>
+          <t>张菁</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>zhoutao</t>
+          <t>zhangjing03</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3926,32 +3861,32 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1688858289869798</t>
+          <t>1688856454985963</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>李秉彰</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>libingzhang</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3963,24 +3898,29 @@
         <v>1</v>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q34" t="n">
         <v>1</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>冯一帆</t>
+          <t>李秉彰</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>fengyifan01</t>
+          <t>libingzhang</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -4025,32 +3965,32 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1688854894759430</t>
+          <t>1688857703847806</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -4062,24 +4002,29 @@
         <v>1</v>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>黄诺</t>
+          <t>卫晓迪</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>huangnuo</t>
+          <t>weixiaodi</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4124,32 +4069,32 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1688854281870561</t>
+          <t>1688854784881059</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -4161,24 +4106,29 @@
         <v>1</v>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>高蕊</t>
+          <t>仲欣琦</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>gaorui01</t>
+          <t>zhongxinqi</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4223,32 +4173,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1688857145762192</t>
+          <t>1688856311853482</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4260,24 +4210,29 @@
         <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>张旭青</t>
+          <t>徐源</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>zhangxuqing</t>
+          <t>xuyuan01</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4322,32 +4277,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1688854497763364</t>
+          <t>1688856454986008</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>杜冠臻</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>duguanzhen</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4359,24 +4314,29 @@
         <v>1</v>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>杨博岚</t>
+          <t>杜冠臻</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>yangbolan</t>
+          <t>duguanzhen</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4421,7 +4381,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1688857167940610</t>
+          <t>1688857752769746</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4436,17 +4396,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4455,27 +4415,27 @@
         </is>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4485,12 +4445,12 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>李欣怡</t>
+          <t>张嘉轩</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>lixinyi02</t>
+          <t>zhangjiaxuan</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4535,32 +4495,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1688856311853482</t>
+          <t>1688854281870561</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4572,29 +4532,24 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>徐源</t>
+          <t>高蕊</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>xuyuan01</t>
+          <t>gaorui01</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4624,7 +4579,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>短期班</t>
+          <t>长期班</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4639,32 +4594,32 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1688855686929440</t>
+          <t>1688856454986129</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>初阶三</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>liwenchao</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4673,12 +4628,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -4689,26 +4639,21 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>杨志杰</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>yangzhijie01</t>
+          <t>liwenchao</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4753,32 +4698,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1688856454986057</t>
+          <t>1688854346851430</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>马元帅</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>mayuanshuai</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4790,29 +4735,29 @@
         <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q42" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>马元帅</t>
+          <t>吕晓菲</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>mayuanshuai</t>
+          <t>lvxiaofei</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4857,32 +4802,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1688858275775684</t>
+          <t>1688854497763364</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>四周测试组</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4901,17 +4846,17 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>刘世乐</t>
+          <t>杨博岚</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>liushile</t>
+          <t>yangbolan</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -4956,7 +4901,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1688855477810382</t>
+          <t>1688855070755789</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4966,22 +4911,22 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4993,10 +4938,20 @@
         <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -5005,12 +4960,12 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>李奕昕</t>
+          <t>严绍源</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>liyixin</t>
+          <t>yanshaoyuan</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -5055,32 +5010,32 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1688854470818602</t>
+          <t>1688858008853709</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -5099,17 +5054,17 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>孙宇哲</t>
+          <t>耿亚轩</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>sunyuzhe</t>
+          <t>gengyaxuan</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -5154,7 +5109,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1688857703847806</t>
+          <t>1688858124858984</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5164,22 +5119,22 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -5191,7 +5146,12 @@
         <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q46" t="n">
         <v>1</v>
@@ -5203,12 +5163,12 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>卫晓迪</t>
+          <t>安怡宣</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>weixiaodi</t>
+          <t>anyixuan</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5253,32 +5213,32 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1688854894759481</t>
+          <t>1688854776688740</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5297,17 +5257,17 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>张宝华</t>
+          <t>张泽栋</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>zhangbaohua01</t>
+          <t>zhangzedong</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5352,32 +5312,32 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1688854894759300</t>
+          <t>1688856665916866</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>郑卓冉</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhengzhuoran</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5389,24 +5349,29 @@
         <v>1</v>
       </c>
       <c r="O48" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>吕禛杨</t>
+          <t>郑卓冉</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>lvzhenyang</t>
+          <t>zhengzhuoran</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5451,7 +5416,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1688855593838985</t>
+          <t>1688857605746717</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5461,22 +5426,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -5488,11 +5453,11 @@
         <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22</t>
+          <t>6,7,8,9,10,11</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -5505,12 +5470,12 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>彭涛</t>
+          <t>郭甜甜</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>pengtao</t>
+          <t>guotiantian</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5555,32 +5520,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1688857790837398</t>
+          <t>1688857254754511</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -5592,29 +5557,24 @@
         <v>1</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>1</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>马浩楠</t>
+          <t>李旭东</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>mahaonan01</t>
+          <t>lixudong</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -5659,32 +5619,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1688854776688740</t>
+          <t>1688857609868354</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -5696,29 +5656,24 @@
         <v>1</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>张泽栋</t>
+          <t>陈跃彬</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>zhangzedong</t>
+          <t>chenyuebin</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -5763,32 +5718,32 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1688858124858906</t>
+          <t>1688857167940616</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>蔺宏业</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>linhongye</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -5797,42 +5752,27 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>刘晓娜</t>
+          <t>蔺宏业</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>liuxiaona</t>
+          <t>linhongye</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -5877,7 +5817,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1688857115860438</t>
+          <t>1688857167940637</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5887,22 +5827,22 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5911,13 +5851,28 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5926,12 +5881,12 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>李仕存</t>
+          <t>沈宇心</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>lishicun</t>
+          <t>shenyuxin</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -5976,7 +5931,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1688857751871228</t>
+          <t>1688855928851644</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5986,22 +5941,22 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -6025,12 +5980,12 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>汪光磊</t>
+          <t>杨璐</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>wangguanglei</t>
+          <t>yanglu</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -6075,7 +6030,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1688854281870599</t>
+          <t>1688857167940654</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -6085,22 +6040,22 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -6112,15 +6067,15 @@
         <v>1</v>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q55" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -6129,12 +6084,12 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>秦思雨</t>
+          <t>野艳红</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>qinsiyu01</t>
+          <t>yeyanhong</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -6179,7 +6134,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1688854522754143</t>
+          <t>1688858124858856</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6189,22 +6144,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -6228,12 +6183,12 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>张波</t>
+          <t>王佳琦</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>zhangbo</t>
+          <t>wangjiaqi05</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -6278,32 +6233,32 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1688855270890512</t>
+          <t>1688857751871228</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>四周测试组</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6322,17 +6277,17 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>浦岩岩</t>
+          <t>汪光磊</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>puyanyan</t>
+          <t>wangguanglei</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -6377,32 +6332,32 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1688857047921497</t>
+          <t>1688858275775684</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>纪覃思</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>jitansi</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6414,29 +6369,24 @@
         <v>1</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
         <v>1</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>纪覃思</t>
+          <t>刘世乐</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>jitansi</t>
+          <t>liushile</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -6481,7 +6431,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1688855639780332</t>
+          <t>1688856261784494</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -6491,22 +6441,22 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6518,7 +6468,12 @@
         <v>1</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q59" t="n">
         <v>1</v>
@@ -6530,12 +6485,12 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>杨寿鑫</t>
+          <t>孟思楠</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>yangshouxin</t>
+          <t>mengsinan</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -6580,7 +6535,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1688854706800124</t>
+          <t>1688857392814199</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -6595,17 +6550,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -6617,7 +6572,12 @@
         <v>1</v>
       </c>
       <c r="O60" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -6629,12 +6589,12 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>杨文昭</t>
+          <t>申谭谭</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>yangwenzhao</t>
+          <t>shentantan</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -6679,7 +6639,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1688857452809589</t>
+          <t>1688857790837398</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -6689,22 +6649,22 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6728,12 +6688,12 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>张硕研</t>
+          <t>马浩楠</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>zhangshuoyan</t>
+          <t>mahaonan01</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -6778,32 +6738,32 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1688855051855742</t>
+          <t>1688855960978536</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>武金贤</t>
+          <t>李志辉</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>wujinxian</t>
+          <t>lizhihui03</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6812,12 +6772,7 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -6828,26 +6783,21 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>武金贤</t>
+          <t>李志辉</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>wujinxian</t>
+          <t>lizhihui03</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -6892,32 +6842,32 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1688856475868784</t>
+          <t>1688854470818602</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -6929,29 +6879,24 @@
         <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>1</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>胡洋铭</t>
+          <t>孙宇哲</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>huyangming</t>
+          <t>sunyuzhe</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -6996,32 +6941,32 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1688858199721276</t>
+          <t>1688854281870539</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -7033,24 +6978,29 @@
         <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>赵静静</t>
+          <t>程佳帅</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>zhaojingjing</t>
+          <t>chengjiashuai</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -7095,7 +7045,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1688854603884803</t>
+          <t>1688855086834341</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -7110,17 +7060,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -7144,12 +7094,12 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>曹添傲</t>
+          <t>魏晨阳</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>caotianao</t>
+          <t>weichenyang</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -7194,32 +7144,32 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1688855292870141</t>
+          <t>1688857452809589</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -7228,42 +7178,27 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>6,7,8,9,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>6,7,8,9,14,15,16,17,18,19</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>赵世文</t>
+          <t>张硕研</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>zhaoshiwen</t>
+          <t>zhangshuoyan</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -7308,32 +7243,32 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1688856665916872</t>
+          <t>1688857790837033</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>张峻玮</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>zhangjunwei01</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7357,17 +7292,17 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>张峻玮</t>
+          <t>张心驰</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>zhangjunwei01</t>
+          <t>zhangxinchi</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -7412,32 +7347,32 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1688856454985976</t>
+          <t>1688854603884803</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>张倩希</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>zhangqianxi</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7446,42 +7381,32 @@
         </is>
       </c>
       <c r="M68" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>张倩希</t>
+          <t>曹添傲</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>zhangqianxi</t>
+          <t>caotianao</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -7526,32 +7451,32 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1688855051855847</t>
+          <t>1688854761929635</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>王安冉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>wanganran</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7563,11 +7488,11 @@
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -7575,17 +7500,17 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>王安冉</t>
+          <t>张亦浩</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>wanganran</t>
+          <t>zhangyihao</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -7630,7 +7555,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1688856454986008</t>
+          <t>1688856454986646</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -7645,17 +7570,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>杜冠臻</t>
+          <t>陈仪薇</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>duguanzhen</t>
+          <t>chenyiwei</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7684,12 +7609,12 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>杜冠臻</t>
+          <t>陈仪薇</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>duguanzhen</t>
+          <t>chenyiwei</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
@@ -7734,32 +7659,32 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1688854784881034</t>
+          <t>1688854894759430</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7771,29 +7696,24 @@
         <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>任超悦</t>
+          <t>黄诺</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>renchaoyue</t>
+          <t>huangnuo</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -7838,32 +7758,32 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1688857790837033</t>
+          <t>1688857691776053</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7875,29 +7795,24 @@
         <v>1</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q72" t="n">
         <v>1</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>张心驰</t>
+          <t>张亮亮</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>zhangxinchi</t>
+          <t>zhangliangliang</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -7942,32 +7857,32 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1688857691776053</t>
+          <t>1688856454986057</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>马元帅</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>mayuanshuai</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7986,17 +7901,17 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>张亮亮</t>
+          <t>马元帅</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>zhangliangliang</t>
+          <t>mayuanshuai</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -8041,32 +7956,32 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1688856665916866</t>
+          <t>1688856920865401</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>郑卓冉</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>zhengzhuoran</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -8078,11 +7993,11 @@
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,12</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -8090,17 +8005,17 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>郑卓冉</t>
+          <t>刘晓松</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>zhengzhuoran</t>
+          <t>liuxiaosong</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -8145,32 +8060,32 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1688857167940616</t>
+          <t>1688854784881054</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>蔺宏业</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>linhongye</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -8179,27 +8094,42 @@
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13</t>
+        </is>
       </c>
       <c r="Q75" t="n">
-        <v>1</v>
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12</t>
+        </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>蔺宏业</t>
+          <t>李梦瑶</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>linhongye</t>
+          <t>limengyao03</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -8244,32 +8174,32 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1688856454985963</t>
+          <t>1688854287853891</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>李秉彰</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>libingzhang</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -8281,29 +8211,24 @@
         <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q76" t="n">
         <v>1</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>李秉彰</t>
+          <t>牛威</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>libingzhang</t>
+          <t>niuwei</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -8348,32 +8273,32 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1688855564781214</t>
+          <t>1688857115860438</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -8392,17 +8317,17 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>陈利辉</t>
+          <t>李仕存</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>chenlihui</t>
+          <t>lishicun</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -8447,7 +8372,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1688854281870530</t>
+          <t>1688854522754143</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -8457,22 +8382,22 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -8496,12 +8421,12 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>赵小漫</t>
+          <t>张波</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>zhaoxiaoman</t>
+          <t>zhangbo</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -8561,7 +8486,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -8650,32 +8575,32 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1688854572834470</t>
+          <t>1688854498774486</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8694,17 +8619,17 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>张浩</t>
+          <t>高梓慧</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>zhanghao06</t>
+          <t>gaozihui</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -8749,32 +8674,32 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1688855086834341</t>
+          <t>1688854260743321</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8793,17 +8718,17 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>魏晨阳</t>
+          <t>杨鹏飞</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>weichenyang</t>
+          <t>yangpengfei</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -8848,32 +8773,32 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1688854287853891</t>
+          <t>1688857167940610</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8885,24 +8810,29 @@
         <v>1</v>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q82" t="n">
         <v>1</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>牛威</t>
+          <t>李欣怡</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>niuwei</t>
+          <t>lixinyi02</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -8947,32 +8877,32 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1688854281870550</t>
+          <t>1688855581862225</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8981,42 +8911,32 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>王紫东</t>
+          <t>张子璇</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>wangzidong</t>
+          <t>zhangzixuan03</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -9061,32 +8981,32 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1688854784881059</t>
+          <t>1688854572834470</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -9098,29 +9018,24 @@
         <v>1</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>仲欣琦</t>
+          <t>张浩</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>zhongxinqi</t>
+          <t>zhanghao06</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -9165,32 +9080,32 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1688857790837332</t>
+          <t>1688854784881036</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -9202,11 +9117,11 @@
         <v>1</v>
       </c>
       <c r="O85" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -9214,17 +9129,17 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>张冰心</t>
+          <t>闫欣雨</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>zhangbingxin</t>
+          <t>yanxinyu</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -9269,32 +9184,32 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1688857609868354</t>
+          <t>1688855639780332</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -9313,17 +9228,17 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>陈跃彬</t>
+          <t>杨寿鑫</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>chenyuebin</t>
+          <t>yangshouxin</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -9368,32 +9283,32 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1688856261784534</t>
+          <t>1688854784881058</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9417,17 +9332,17 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>刘佳欣</t>
+          <t>翟林志</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>liujiaxin01</t>
+          <t>zhailinzhi</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -9472,32 +9387,32 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1688857751871196</t>
+          <t>1688854894759300</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9509,29 +9424,24 @@
         <v>1</v>
       </c>
       <c r="O88" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>1</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>杨佳雪</t>
+          <t>吕禛杨</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>yangjiaxue</t>
+          <t>lvzhenyang</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -9576,32 +9486,32 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1688854784881036</t>
+          <t>1688854281870550</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9613,29 +9523,24 @@
         <v>1</v>
       </c>
       <c r="O89" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>13,14,15,16,17</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q89" t="n">
         <v>1</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>闫欣雨</t>
+          <t>王紫东</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>yanxinyu</t>
+          <t>wangzidong</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -9680,32 +9585,32 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1688856995795370</t>
+          <t>1688857751871196</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -9724,17 +9629,17 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>赵晨曦</t>
+          <t>杨佳雪</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>zhaochenxi</t>
+          <t>yangjiaxue</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -9779,32 +9684,32 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1688858124858984</t>
+          <t>1688856995795370</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -9823,17 +9728,17 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>安怡宣</t>
+          <t>赵晨曦</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>anyixuan</t>
+          <t>zhaochenxi</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -9878,32 +9783,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1688857752769746</t>
+          <t>1688854287853916</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>四周测试组</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9912,42 +9817,42 @@
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>张嘉轩</t>
+          <t>谷豪华</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>zhangjiaxuan</t>
+          <t>guhaohua</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -9992,32 +9897,32 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1688857167940637</t>
+          <t>1688856665916872</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>张峻玮</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>zhangjunwei01</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -10041,17 +9946,17 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>沈宇心</t>
+          <t>张峻玮</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>shenyuxin</t>
+          <t>zhangjunwei01</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
@@ -10096,32 +10001,32 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1688854281870539</t>
+          <t>1688855686929440</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>WFCPeak</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -10133,29 +10038,24 @@
         <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q94" t="n">
         <v>1</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>程佳帅</t>
+          <t>杨志杰</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>chengjiashuai</t>
+          <t>yangzhijie01</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -10200,32 +10100,32 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1688854815837469</t>
+          <t>1688856261784534</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>旺旺麦旋风</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -10237,24 +10137,29 @@
         <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q95" t="n">
         <v>1</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>张菁</t>
+          <t>刘佳欣</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>zhangjing03</t>
+          <t>liujiaxin01</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
@@ -10299,32 +10204,32 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1688856454986129</t>
+          <t>1688857790837332</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>李文超</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>liwenchao</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -10333,12 +10238,7 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -10349,26 +10249,21 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>李文超</t>
+          <t>张冰心</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>liwenchao</t>
+          <t>zhangbingxin</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
@@ -10413,32 +10308,32 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1688857392814199</t>
+          <t>1688854784881034</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10450,24 +10345,29 @@
         <v>1</v>
       </c>
       <c r="O97" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q97" t="n">
         <v>1</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>申谭谭</t>
+          <t>任超悦</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>shentantan</t>
+          <t>renchaoyue</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
@@ -10512,32 +10412,32 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1688854894759558</t>
+          <t>1688858289869798</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10549,24 +10449,29 @@
         <v>1</v>
       </c>
       <c r="O98" t="n">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,20,23</t>
+        </is>
       </c>
       <c r="Q98" t="n">
         <v>1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>胡茹茹</t>
+          <t>冯一帆</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>hururu</t>
+          <t>fengyifan01</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -10611,32 +10516,32 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1688854784881054</t>
+          <t>1688856644818249</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>秋拾</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10648,29 +10553,29 @@
         <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>李梦瑶</t>
+          <t>郭少华</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>limengyao03</t>
+          <t>guoshaohua</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -10715,32 +10620,32 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1688856665916876</t>
+          <t>1688858124858906</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>朱玉聪</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>zhuyucong</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10752,29 +10657,29 @@
         <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>朱玉聪</t>
+          <t>刘晓娜</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>zhuyucong</t>
+          <t>liuxiaona</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -10819,32 +10724,32 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1688855270890491</t>
+          <t>1688857460767926</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>重装九组</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -10856,24 +10761,29 @@
         <v>1</v>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>10,11,12</t>
+        </is>
       </c>
       <c r="Q101" t="n">
         <v>1</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>郭佳浩</t>
+          <t>季子傲</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>guojiahao</t>
+          <t>jiziao</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -10918,32 +10828,32 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1688854761929635</t>
+          <t>1688855051855742</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -10955,11 +10865,11 @@
         <v>1</v>
       </c>
       <c r="O102" t="n">
-        <v>0.7222222222222222</v>
+        <v>0</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>8,9,10,11,12</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -10967,17 +10877,17 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>达播</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>张亦浩</t>
+          <t>武金贤</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>zhangyihao</t>
+          <t>wujinxian</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -11022,32 +10932,32 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1688855270890436</t>
+          <t>1688855564781214</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -11056,42 +10966,27 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R103" t="inlineStr">
-        <is>
-          <t>20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>张学伦</t>
+          <t>陈利辉</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>zhangxuelun01</t>
+          <t>chenlihui</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -11136,32 +11031,32 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1688855581862225</t>
+          <t>1688855270890436</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -11173,29 +11068,24 @@
         <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>张子璇</t>
+          <t>张学伦</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>zhangzixuan03</t>
+          <t>zhangxuelun01</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -11240,7 +11130,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1688856819940740</t>
+          <t>1688854287853876</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -11250,22 +11140,22 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>秋拾</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -11277,7 +11167,12 @@
         <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>8,9,10,11,12</t>
+        </is>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -11289,12 +11184,12 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>芦凯</t>
+          <t>董宇波</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>lukai</t>
+          <t>dongyubo</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -11339,32 +11234,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1688856454985988</t>
+          <t>1688857372708211</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>白肖阳</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>baixiaoyang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -11373,42 +11268,32 @@
         </is>
       </c>
       <c r="M106" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O106" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>12,13,14</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R106" t="inlineStr">
-        <is>
-          <t>12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>白肖阳</t>
+          <t>崔玉婷</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>baixiaoyang</t>
+          <t>cuiyuting</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -11453,32 +11338,32 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1688854287853916</t>
+          <t>1688856665916876</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>朱玉聪</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhuyucong</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -11490,11 +11375,11 @@
         <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>10,11</t>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -11502,17 +11387,17 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>谷豪华</t>
+          <t>朱玉聪</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>guhaohua</t>
+          <t>zhuyucong</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -11557,32 +11442,32 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1688857047921523</t>
+          <t>1688854476856420</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>王姿</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>wangzi</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -11594,11 +11479,11 @@
         <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -11606,17 +11491,17 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>王姿</t>
+          <t>李雨薇</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>wangzi</t>
+          <t>liyuwei</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -11630,214 +11515,6 @@
         </is>
       </c>
       <c r="X108" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
-        <v>20261023</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>初阶</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1688856454986646</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>新兵营-出</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>陈仪薇</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>chenyiwei</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M109" t="n">
-        <v>1</v>
-      </c>
-      <c r="O109" t="n">
-        <v>0</v>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q109" t="n">
-        <v>1</v>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T109" t="inlineStr">
-        <is>
-          <t>陈仪薇</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
-        <is>
-          <t>chenyiwei</t>
-        </is>
-      </c>
-      <c r="V109" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W109" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>石家庄初短</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
-        <v>20261023</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>石家庄</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>短期班</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>初阶</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1688857167940654</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>新兵营彬</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>野艳红</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>yeyanhong</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>低价课</t>
-        </is>
-      </c>
-      <c r="M110" t="n">
-        <v>1</v>
-      </c>
-      <c r="O110" t="n">
-        <v>0</v>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
-      </c>
-      <c r="Q110" t="n">
-        <v>1</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>新兵营</t>
-        </is>
-      </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>野艳红</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
-        <is>
-          <t>yeyanhong</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>爱学</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
         <is>
           <t>石家庄初短</t>
         </is>
@@ -11854,7 +11531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11907,28 +11584,28 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -11939,28 +11616,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>数学199</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
+          <t>初三 汇总</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8888888888888888</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -11976,23 +11649,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="5">
@@ -12003,24 +11676,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>数学199 汇总</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>数学199</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>四周测试组</t>
+        </is>
+      </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -12031,28 +11708,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8461538461538461</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="7">
@@ -12063,28 +11740,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="8">
@@ -12095,24 +11772,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>数学99 汇总</t>
+          <t>数学199 汇总</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E8" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="G8" t="n">
         <v>25</v>
       </c>
-      <c r="E8" t="n">
-        <v>23</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G8" t="n">
-        <v>14</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="9">
@@ -12123,28 +11800,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="10">
@@ -12155,28 +11832,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -12187,24 +11864,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
+          <t>数学99 汇总</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E11" t="n">
         <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.5185185185185185</v>
       </c>
     </row>
     <row r="12">
@@ -12215,28 +11892,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>达播</t>
+          <t>新兵营</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WFCPeak</t>
+          <t>新兵营-出</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>21</v>
+      </c>
+      <c r="E12" t="n">
         <v>13</v>
       </c>
-      <c r="E12" t="n">
-        <v>9</v>
-      </c>
       <c r="F12" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.09523809523809523</v>
       </c>
     </row>
     <row r="13">
@@ -12247,28 +11924,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>达播</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>秋拾</t>
-        </is>
-      </c>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4</v>
+        <v>0.09523809523809523</v>
       </c>
     </row>
     <row r="14">
@@ -12279,24 +11952,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>达播 汇总</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>达播</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WFCPeak</t>
+        </is>
+      </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7826086956521739</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4782608695652174</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
@@ -12307,24 +11984,116 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>达播</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>旺旺麦旋风</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>达播</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>秋拾</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>达播 汇总</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>初中 汇总</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="n">
-        <v>109</v>
-      </c>
-      <c r="E15" t="n">
-        <v>92</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.8440366972477065</v>
-      </c>
-      <c r="G15" t="n">
-        <v>50</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.4587155963302753</v>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>118</v>
+      </c>
+      <c r="E18" t="n">
+        <v>99</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8389830508474576</v>
+      </c>
+      <c r="G18" t="n">
+        <v>55</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4661016949152542</v>
       </c>
     </row>
   </sheetData>
@@ -12338,7 +12107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12354,7 +12123,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（石家庄初短）-10月19日</t>
+          <t>企微风灵全天在线情况通晒（石家庄初短）-10月21日</t>
         </is>
       </c>
     </row>
@@ -12426,60 +12195,56 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>数学199</t>
+          <t>初三</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>云程发轫</t>
+          <t>李文超</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.7777777777777778</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>数学199</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>重装九组</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>0.8888888888888888</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>初三 汇总</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr"/>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -12495,51 +12260,55 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>重装五组</t>
+          <t>云程发轫</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>数学199 汇总</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0.9032258064516129</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0.7096774193548387</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>数学199</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>四周测试组</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -12550,28 +12319,28 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>天天向上</t>
+          <t>重装九组</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.8461538461538461</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="9">
@@ -12582,28 +12351,28 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>数学99</t>
+          <t>数学199</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>超级莱米</t>
+          <t>重装五组</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>12</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7692307692307693</v>
       </c>
     </row>
     <row r="10">
@@ -12614,24 +12383,24 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>数学99 汇总</t>
+          <t>数学199 汇总</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E10" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>14</v>
-      </c>
       <c r="H10" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="11">
@@ -12642,28 +12411,28 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>新兵营-出</t>
+          <t>天天向上</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -12674,28 +12443,28 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>新兵营</t>
+          <t>数学99</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>新兵营彬</t>
+          <t>超级莱米</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>1</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
@@ -12706,24 +12475,24 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>新兵营 汇总</t>
+          <t>数学99 汇总</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr"/>
       <c r="D13" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>23</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.1</v>
+        <v>0.5185185185185185</v>
       </c>
     </row>
     <row r="14">
@@ -12734,116 +12503,208 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>新兵营</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>新兵营-出</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>新兵营 汇总</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>达播</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>WFCPeak</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="D16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="G16" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="F14" s="5" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="H16" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>达播</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>旺旺麦旋风</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.2222222222222222</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>达播</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>秋拾</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="5" t="n">
+      <c r="D18" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>达播 汇总</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr"/>
+      <c r="D19" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="7" t="n">
         <v>0.4</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>达播 汇总</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr"/>
-      <c r="D16" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>0.7826086956521739</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0.4782608695652174</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>初中</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>初中 汇总</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="6" t="n">
-        <v>109</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0.8440366972477065</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0.4587155963302753</v>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="n">
+        <v>118</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0.8389830508474576</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.4661016949152542</v>
       </c>
     </row>
   </sheetData>
